--- a/perill_diagnostic.xlsx
+++ b/perill_diagnostic.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacky/Desktop/HPT_perill_app/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CAYJAYI\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2511E6E-C052-6F44-B23A-FFFA5551993D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DC39F2-11BE-4072-B037-96E3DD04AEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14430" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" r:id="rId1"/>
     <sheet name="Responses" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="75">
   <si>
     <t>Departments</t>
   </si>
@@ -240,6 +253,12 @@
   </si>
   <si>
     <t>2026-05-23 19:21:05</t>
+  </si>
+  <si>
+    <t>Digital Experience</t>
+  </si>
+  <si>
+    <t>Global Business Services</t>
   </si>
 </sst>
 </file>
@@ -584,94 +603,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -683,14 +702,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AX62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AX100"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7265625" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -842,12 +861,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C2">
         <v>8</v>
@@ -994,7 +1013,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -1146,12 +1165,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1298,12 +1317,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -1450,7 +1469,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>72</v>
       </c>
@@ -1602,12 +1621,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1754,12 +1773,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1906,12 +1925,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -2058,12 +2077,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -2210,12 +2229,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -2362,12 +2381,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -2514,12 +2533,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2666,12 +2685,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C14">
         <v>9</v>
@@ -2818,12 +2837,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B15" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -2970,12 +2989,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B16" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -3122,12 +3141,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B17" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C17">
         <v>9</v>
@@ -3274,12 +3293,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B18" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C18">
         <v>8</v>
@@ -3426,12 +3445,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B19" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C19">
         <v>10</v>
@@ -3578,12 +3597,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B20" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -3730,12 +3749,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B21" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C21">
         <v>8</v>
@@ -3882,12 +3901,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B22" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C22">
         <v>7</v>
@@ -4034,12 +4053,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B23" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -4186,12 +4205,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B24" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C24">
         <v>7</v>
@@ -4338,12 +4357,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>46165.833344907413</v>
       </c>
       <c r="B25" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C25">
         <v>10</v>
@@ -4490,7 +4509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -4642,7 +4661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -4794,7 +4813,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -4946,7 +4965,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -5098,7 +5117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -5250,7 +5269,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -5402,7 +5421,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -5554,7 +5573,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -5706,7 +5725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -5858,7 +5877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -6010,7 +6029,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -6162,7 +6181,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -6314,7 +6333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -6466,7 +6485,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -6618,7 +6637,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -6770,7 +6789,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -6922,7 +6941,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -7074,7 +7093,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -7226,7 +7245,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>46165.875057870369</v>
       </c>
@@ -7378,7 +7397,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -7530,7 +7549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -7682,7 +7701,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -7834,7 +7853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -7986,7 +8005,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -8138,7 +8157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -8290,7 +8309,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -8442,7 +8461,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -8594,7 +8613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -8746,7 +8765,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -8898,7 +8917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -9050,7 +9069,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -9202,7 +9221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -9354,7 +9373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -9506,7 +9525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -9658,7 +9677,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -9810,7 +9829,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -9962,7 +9981,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>46165.916724537034</v>
       </c>
@@ -10112,6 +10131,5782 @@
       </c>
       <c r="AX62">
         <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A63" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B63" t="s">
+        <v>74</v>
+      </c>
+      <c r="C63">
+        <v>7</v>
+      </c>
+      <c r="D63">
+        <v>2</v>
+      </c>
+      <c r="E63">
+        <v>3</v>
+      </c>
+      <c r="F63">
+        <v>7</v>
+      </c>
+      <c r="G63">
+        <v>8</v>
+      </c>
+      <c r="H63">
+        <v>8</v>
+      </c>
+      <c r="I63">
+        <v>10</v>
+      </c>
+      <c r="J63">
+        <v>4</v>
+      </c>
+      <c r="K63">
+        <v>9</v>
+      </c>
+      <c r="L63">
+        <v>3</v>
+      </c>
+      <c r="M63">
+        <v>4</v>
+      </c>
+      <c r="N63">
+        <v>6</v>
+      </c>
+      <c r="O63">
+        <v>5</v>
+      </c>
+      <c r="P63">
+        <v>9</v>
+      </c>
+      <c r="Q63">
+        <v>6</v>
+      </c>
+      <c r="R63">
+        <v>6</v>
+      </c>
+      <c r="S63">
+        <v>5</v>
+      </c>
+      <c r="T63">
+        <v>5</v>
+      </c>
+      <c r="U63">
+        <v>10</v>
+      </c>
+      <c r="V63">
+        <v>3</v>
+      </c>
+      <c r="W63">
+        <v>2</v>
+      </c>
+      <c r="X63">
+        <v>2</v>
+      </c>
+      <c r="Y63">
+        <v>3</v>
+      </c>
+      <c r="Z63">
+        <v>4</v>
+      </c>
+      <c r="AA63">
+        <v>1</v>
+      </c>
+      <c r="AB63">
+        <v>7</v>
+      </c>
+      <c r="AC63">
+        <v>10</v>
+      </c>
+      <c r="AD63">
+        <v>2</v>
+      </c>
+      <c r="AE63">
+        <v>5</v>
+      </c>
+      <c r="AF63">
+        <v>2</v>
+      </c>
+      <c r="AG63">
+        <v>8</v>
+      </c>
+      <c r="AH63">
+        <v>1</v>
+      </c>
+      <c r="AI63">
+        <v>10</v>
+      </c>
+      <c r="AJ63">
+        <v>6</v>
+      </c>
+      <c r="AK63">
+        <v>10</v>
+      </c>
+      <c r="AL63">
+        <v>1</v>
+      </c>
+      <c r="AM63">
+        <v>2</v>
+      </c>
+      <c r="AN63">
+        <v>5</v>
+      </c>
+      <c r="AO63">
+        <v>7</v>
+      </c>
+      <c r="AP63">
+        <v>7</v>
+      </c>
+      <c r="AQ63">
+        <v>9</v>
+      </c>
+      <c r="AR63">
+        <v>10</v>
+      </c>
+      <c r="AS63">
+        <v>5</v>
+      </c>
+      <c r="AT63">
+        <v>5</v>
+      </c>
+      <c r="AU63">
+        <v>9</v>
+      </c>
+      <c r="AV63">
+        <v>6</v>
+      </c>
+      <c r="AW63">
+        <v>8</v>
+      </c>
+      <c r="AX63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A64" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B64" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64">
+        <v>8</v>
+      </c>
+      <c r="E64">
+        <v>5</v>
+      </c>
+      <c r="F64">
+        <v>7</v>
+      </c>
+      <c r="G64">
+        <v>9</v>
+      </c>
+      <c r="H64">
+        <v>7</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>7</v>
+      </c>
+      <c r="K64">
+        <v>10</v>
+      </c>
+      <c r="L64">
+        <v>2</v>
+      </c>
+      <c r="M64">
+        <v>3</v>
+      </c>
+      <c r="N64">
+        <v>4</v>
+      </c>
+      <c r="O64">
+        <v>6</v>
+      </c>
+      <c r="P64">
+        <v>2</v>
+      </c>
+      <c r="Q64">
+        <v>8</v>
+      </c>
+      <c r="R64">
+        <v>10</v>
+      </c>
+      <c r="S64">
+        <v>5</v>
+      </c>
+      <c r="T64">
+        <v>9</v>
+      </c>
+      <c r="U64">
+        <v>6</v>
+      </c>
+      <c r="V64">
+        <v>2</v>
+      </c>
+      <c r="W64">
+        <v>9</v>
+      </c>
+      <c r="X64">
+        <v>2</v>
+      </c>
+      <c r="Y64">
+        <v>4</v>
+      </c>
+      <c r="Z64">
+        <v>4</v>
+      </c>
+      <c r="AA64">
+        <v>6</v>
+      </c>
+      <c r="AB64">
+        <v>6</v>
+      </c>
+      <c r="AC64">
+        <v>9</v>
+      </c>
+      <c r="AD64">
+        <v>4</v>
+      </c>
+      <c r="AE64">
+        <v>10</v>
+      </c>
+      <c r="AF64">
+        <v>5</v>
+      </c>
+      <c r="AG64">
+        <v>9</v>
+      </c>
+      <c r="AH64">
+        <v>3</v>
+      </c>
+      <c r="AI64">
+        <v>4</v>
+      </c>
+      <c r="AJ64">
+        <v>10</v>
+      </c>
+      <c r="AK64">
+        <v>7</v>
+      </c>
+      <c r="AL64">
+        <v>6</v>
+      </c>
+      <c r="AM64">
+        <v>9</v>
+      </c>
+      <c r="AN64">
+        <v>4</v>
+      </c>
+      <c r="AO64">
+        <v>7</v>
+      </c>
+      <c r="AP64">
+        <v>9</v>
+      </c>
+      <c r="AQ64">
+        <v>1</v>
+      </c>
+      <c r="AR64">
+        <v>3</v>
+      </c>
+      <c r="AS64">
+        <v>2</v>
+      </c>
+      <c r="AT64">
+        <v>5</v>
+      </c>
+      <c r="AU64">
+        <v>3</v>
+      </c>
+      <c r="AV64">
+        <v>5</v>
+      </c>
+      <c r="AW64">
+        <v>10</v>
+      </c>
+      <c r="AX64">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A65" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B65" t="s">
+        <v>74</v>
+      </c>
+      <c r="C65">
+        <v>10</v>
+      </c>
+      <c r="D65">
+        <v>8</v>
+      </c>
+      <c r="E65">
+        <v>6</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>7</v>
+      </c>
+      <c r="H65">
+        <v>6</v>
+      </c>
+      <c r="I65">
+        <v>10</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65">
+        <v>7</v>
+      </c>
+      <c r="L65">
+        <v>1</v>
+      </c>
+      <c r="M65">
+        <v>9</v>
+      </c>
+      <c r="N65">
+        <v>6</v>
+      </c>
+      <c r="O65">
+        <v>5</v>
+      </c>
+      <c r="P65">
+        <v>10</v>
+      </c>
+      <c r="Q65">
+        <v>10</v>
+      </c>
+      <c r="R65">
+        <v>4</v>
+      </c>
+      <c r="S65">
+        <v>6</v>
+      </c>
+      <c r="T65">
+        <v>3</v>
+      </c>
+      <c r="U65">
+        <v>1</v>
+      </c>
+      <c r="V65">
+        <v>4</v>
+      </c>
+      <c r="W65">
+        <v>4</v>
+      </c>
+      <c r="X65">
+        <v>6</v>
+      </c>
+      <c r="Y65">
+        <v>4</v>
+      </c>
+      <c r="Z65">
+        <v>3</v>
+      </c>
+      <c r="AA65">
+        <v>9</v>
+      </c>
+      <c r="AB65">
+        <v>9</v>
+      </c>
+      <c r="AC65">
+        <v>8</v>
+      </c>
+      <c r="AD65">
+        <v>10</v>
+      </c>
+      <c r="AE65">
+        <v>10</v>
+      </c>
+      <c r="AF65">
+        <v>2</v>
+      </c>
+      <c r="AG65">
+        <v>5</v>
+      </c>
+      <c r="AH65">
+        <v>3</v>
+      </c>
+      <c r="AI65">
+        <v>9</v>
+      </c>
+      <c r="AJ65">
+        <v>8</v>
+      </c>
+      <c r="AK65">
+        <v>6</v>
+      </c>
+      <c r="AL65">
+        <v>1</v>
+      </c>
+      <c r="AM65">
+        <v>6</v>
+      </c>
+      <c r="AN65">
+        <v>8</v>
+      </c>
+      <c r="AO65">
+        <v>9</v>
+      </c>
+      <c r="AP65">
+        <v>6</v>
+      </c>
+      <c r="AQ65">
+        <v>5</v>
+      </c>
+      <c r="AR65">
+        <v>4</v>
+      </c>
+      <c r="AS65">
+        <v>5</v>
+      </c>
+      <c r="AT65">
+        <v>3</v>
+      </c>
+      <c r="AU65">
+        <v>4</v>
+      </c>
+      <c r="AV65">
+        <v>9</v>
+      </c>
+      <c r="AW65">
+        <v>10</v>
+      </c>
+      <c r="AX65">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A66" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B66" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66">
+        <v>9</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+      <c r="E66">
+        <v>10</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66">
+        <v>6</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>4</v>
+      </c>
+      <c r="J66">
+        <v>2</v>
+      </c>
+      <c r="K66">
+        <v>8</v>
+      </c>
+      <c r="L66">
+        <v>6</v>
+      </c>
+      <c r="M66">
+        <v>6</v>
+      </c>
+      <c r="N66">
+        <v>5</v>
+      </c>
+      <c r="O66">
+        <v>4</v>
+      </c>
+      <c r="P66">
+        <v>10</v>
+      </c>
+      <c r="Q66">
+        <v>2</v>
+      </c>
+      <c r="R66">
+        <v>4</v>
+      </c>
+      <c r="S66">
+        <v>4</v>
+      </c>
+      <c r="T66">
+        <v>4</v>
+      </c>
+      <c r="U66">
+        <v>4</v>
+      </c>
+      <c r="V66">
+        <v>2</v>
+      </c>
+      <c r="W66">
+        <v>9</v>
+      </c>
+      <c r="X66">
+        <v>7</v>
+      </c>
+      <c r="Y66">
+        <v>6</v>
+      </c>
+      <c r="Z66">
+        <v>2</v>
+      </c>
+      <c r="AA66">
+        <v>2</v>
+      </c>
+      <c r="AB66">
+        <v>6</v>
+      </c>
+      <c r="AC66">
+        <v>2</v>
+      </c>
+      <c r="AD66">
+        <v>2</v>
+      </c>
+      <c r="AE66">
+        <v>2</v>
+      </c>
+      <c r="AF66">
+        <v>1</v>
+      </c>
+      <c r="AG66">
+        <v>2</v>
+      </c>
+      <c r="AH66">
+        <v>8</v>
+      </c>
+      <c r="AI66">
+        <v>9</v>
+      </c>
+      <c r="AJ66">
+        <v>1</v>
+      </c>
+      <c r="AK66">
+        <v>4</v>
+      </c>
+      <c r="AL66">
+        <v>7</v>
+      </c>
+      <c r="AM66">
+        <v>8</v>
+      </c>
+      <c r="AN66">
+        <v>1</v>
+      </c>
+      <c r="AO66">
+        <v>1</v>
+      </c>
+      <c r="AP66">
+        <v>8</v>
+      </c>
+      <c r="AQ66">
+        <v>3</v>
+      </c>
+      <c r="AR66">
+        <v>10</v>
+      </c>
+      <c r="AS66">
+        <v>8</v>
+      </c>
+      <c r="AT66">
+        <v>1</v>
+      </c>
+      <c r="AU66">
+        <v>2</v>
+      </c>
+      <c r="AV66">
+        <v>5</v>
+      </c>
+      <c r="AW66">
+        <v>8</v>
+      </c>
+      <c r="AX66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A67" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B67" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>5</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67">
+        <v>4</v>
+      </c>
+      <c r="H67">
+        <v>4</v>
+      </c>
+      <c r="I67">
+        <v>2</v>
+      </c>
+      <c r="J67">
+        <v>8</v>
+      </c>
+      <c r="K67">
+        <v>10</v>
+      </c>
+      <c r="L67">
+        <v>9</v>
+      </c>
+      <c r="M67">
+        <v>5</v>
+      </c>
+      <c r="N67">
+        <v>10</v>
+      </c>
+      <c r="O67">
+        <v>2</v>
+      </c>
+      <c r="P67">
+        <v>9</v>
+      </c>
+      <c r="Q67">
+        <v>5</v>
+      </c>
+      <c r="R67">
+        <v>1</v>
+      </c>
+      <c r="S67">
+        <v>3</v>
+      </c>
+      <c r="T67">
+        <v>9</v>
+      </c>
+      <c r="U67">
+        <v>6</v>
+      </c>
+      <c r="V67">
+        <v>1</v>
+      </c>
+      <c r="W67">
+        <v>5</v>
+      </c>
+      <c r="X67">
+        <v>5</v>
+      </c>
+      <c r="Y67">
+        <v>6</v>
+      </c>
+      <c r="Z67">
+        <v>4</v>
+      </c>
+      <c r="AA67">
+        <v>6</v>
+      </c>
+      <c r="AB67">
+        <v>6</v>
+      </c>
+      <c r="AC67">
+        <v>2</v>
+      </c>
+      <c r="AD67">
+        <v>4</v>
+      </c>
+      <c r="AE67">
+        <v>9</v>
+      </c>
+      <c r="AF67">
+        <v>2</v>
+      </c>
+      <c r="AG67">
+        <v>7</v>
+      </c>
+      <c r="AH67">
+        <v>8</v>
+      </c>
+      <c r="AI67">
+        <v>3</v>
+      </c>
+      <c r="AJ67">
+        <v>9</v>
+      </c>
+      <c r="AK67">
+        <v>5</v>
+      </c>
+      <c r="AL67">
+        <v>10</v>
+      </c>
+      <c r="AM67">
+        <v>9</v>
+      </c>
+      <c r="AN67">
+        <v>10</v>
+      </c>
+      <c r="AO67">
+        <v>1</v>
+      </c>
+      <c r="AP67">
+        <v>2</v>
+      </c>
+      <c r="AQ67">
+        <v>7</v>
+      </c>
+      <c r="AR67">
+        <v>1</v>
+      </c>
+      <c r="AS67">
+        <v>5</v>
+      </c>
+      <c r="AT67">
+        <v>6</v>
+      </c>
+      <c r="AU67">
+        <v>10</v>
+      </c>
+      <c r="AV67">
+        <v>6</v>
+      </c>
+      <c r="AW67">
+        <v>3</v>
+      </c>
+      <c r="AX67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A68" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68">
+        <v>10</v>
+      </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+      <c r="E68">
+        <v>3</v>
+      </c>
+      <c r="F68">
+        <v>5</v>
+      </c>
+      <c r="G68">
+        <v>7</v>
+      </c>
+      <c r="H68">
+        <v>8</v>
+      </c>
+      <c r="I68">
+        <v>9</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68">
+        <v>5</v>
+      </c>
+      <c r="L68">
+        <v>3</v>
+      </c>
+      <c r="M68">
+        <v>10</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68">
+        <v>8</v>
+      </c>
+      <c r="P68">
+        <v>5</v>
+      </c>
+      <c r="Q68">
+        <v>1</v>
+      </c>
+      <c r="R68">
+        <v>5</v>
+      </c>
+      <c r="S68">
+        <v>3</v>
+      </c>
+      <c r="T68">
+        <v>7</v>
+      </c>
+      <c r="U68">
+        <v>9</v>
+      </c>
+      <c r="V68">
+        <v>7</v>
+      </c>
+      <c r="W68">
+        <v>1</v>
+      </c>
+      <c r="X68">
+        <v>8</v>
+      </c>
+      <c r="Y68">
+        <v>6</v>
+      </c>
+      <c r="Z68">
+        <v>10</v>
+      </c>
+      <c r="AA68">
+        <v>6</v>
+      </c>
+      <c r="AB68">
+        <v>4</v>
+      </c>
+      <c r="AC68">
+        <v>7</v>
+      </c>
+      <c r="AD68">
+        <v>7</v>
+      </c>
+      <c r="AE68">
+        <v>1</v>
+      </c>
+      <c r="AF68">
+        <v>10</v>
+      </c>
+      <c r="AG68">
+        <v>9</v>
+      </c>
+      <c r="AH68">
+        <v>10</v>
+      </c>
+      <c r="AI68">
+        <v>4</v>
+      </c>
+      <c r="AJ68">
+        <v>8</v>
+      </c>
+      <c r="AK68">
+        <v>3</v>
+      </c>
+      <c r="AL68">
+        <v>5</v>
+      </c>
+      <c r="AM68">
+        <v>7</v>
+      </c>
+      <c r="AN68">
+        <v>2</v>
+      </c>
+      <c r="AO68">
+        <v>10</v>
+      </c>
+      <c r="AP68">
+        <v>4</v>
+      </c>
+      <c r="AQ68">
+        <v>3</v>
+      </c>
+      <c r="AR68">
+        <v>10</v>
+      </c>
+      <c r="AS68">
+        <v>4</v>
+      </c>
+      <c r="AT68">
+        <v>2</v>
+      </c>
+      <c r="AU68">
+        <v>6</v>
+      </c>
+      <c r="AV68">
+        <v>2</v>
+      </c>
+      <c r="AW68">
+        <v>3</v>
+      </c>
+      <c r="AX68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A69" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B69" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69">
+        <v>4</v>
+      </c>
+      <c r="D69">
+        <v>10</v>
+      </c>
+      <c r="E69">
+        <v>4</v>
+      </c>
+      <c r="F69">
+        <v>4</v>
+      </c>
+      <c r="G69">
+        <v>5</v>
+      </c>
+      <c r="H69">
+        <v>4</v>
+      </c>
+      <c r="I69">
+        <v>3</v>
+      </c>
+      <c r="J69">
+        <v>10</v>
+      </c>
+      <c r="K69">
+        <v>10</v>
+      </c>
+      <c r="L69">
+        <v>4</v>
+      </c>
+      <c r="M69">
+        <v>6</v>
+      </c>
+      <c r="N69">
+        <v>2</v>
+      </c>
+      <c r="O69">
+        <v>7</v>
+      </c>
+      <c r="P69">
+        <v>4</v>
+      </c>
+      <c r="Q69">
+        <v>8</v>
+      </c>
+      <c r="R69">
+        <v>2</v>
+      </c>
+      <c r="S69">
+        <v>5</v>
+      </c>
+      <c r="T69">
+        <v>9</v>
+      </c>
+      <c r="U69">
+        <v>9</v>
+      </c>
+      <c r="V69">
+        <v>5</v>
+      </c>
+      <c r="W69">
+        <v>1</v>
+      </c>
+      <c r="X69">
+        <v>9</v>
+      </c>
+      <c r="Y69">
+        <v>6</v>
+      </c>
+      <c r="Z69">
+        <v>6</v>
+      </c>
+      <c r="AA69">
+        <v>1</v>
+      </c>
+      <c r="AB69">
+        <v>7</v>
+      </c>
+      <c r="AC69">
+        <v>7</v>
+      </c>
+      <c r="AD69">
+        <v>3</v>
+      </c>
+      <c r="AE69">
+        <v>4</v>
+      </c>
+      <c r="AF69">
+        <v>9</v>
+      </c>
+      <c r="AG69">
+        <v>5</v>
+      </c>
+      <c r="AH69">
+        <v>2</v>
+      </c>
+      <c r="AI69">
+        <v>4</v>
+      </c>
+      <c r="AJ69">
+        <v>8</v>
+      </c>
+      <c r="AK69">
+        <v>5</v>
+      </c>
+      <c r="AL69">
+        <v>4</v>
+      </c>
+      <c r="AM69">
+        <v>7</v>
+      </c>
+      <c r="AN69">
+        <v>5</v>
+      </c>
+      <c r="AO69">
+        <v>9</v>
+      </c>
+      <c r="AP69">
+        <v>1</v>
+      </c>
+      <c r="AQ69">
+        <v>10</v>
+      </c>
+      <c r="AR69">
+        <v>1</v>
+      </c>
+      <c r="AS69">
+        <v>3</v>
+      </c>
+      <c r="AT69">
+        <v>4</v>
+      </c>
+      <c r="AU69">
+        <v>7</v>
+      </c>
+      <c r="AV69">
+        <v>1</v>
+      </c>
+      <c r="AW69">
+        <v>9</v>
+      </c>
+      <c r="AX69">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A70" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B70" t="s">
+        <v>74</v>
+      </c>
+      <c r="C70">
+        <v>10</v>
+      </c>
+      <c r="D70">
+        <v>4</v>
+      </c>
+      <c r="E70">
+        <v>2</v>
+      </c>
+      <c r="F70">
+        <v>6</v>
+      </c>
+      <c r="G70">
+        <v>5</v>
+      </c>
+      <c r="H70">
+        <v>5</v>
+      </c>
+      <c r="I70">
+        <v>5</v>
+      </c>
+      <c r="J70">
+        <v>4</v>
+      </c>
+      <c r="K70">
+        <v>10</v>
+      </c>
+      <c r="L70">
+        <v>8</v>
+      </c>
+      <c r="M70">
+        <v>5</v>
+      </c>
+      <c r="N70">
+        <v>5</v>
+      </c>
+      <c r="O70">
+        <v>5</v>
+      </c>
+      <c r="P70">
+        <v>10</v>
+      </c>
+      <c r="Q70">
+        <v>9</v>
+      </c>
+      <c r="R70">
+        <v>9</v>
+      </c>
+      <c r="S70">
+        <v>5</v>
+      </c>
+      <c r="T70">
+        <v>3</v>
+      </c>
+      <c r="U70">
+        <v>6</v>
+      </c>
+      <c r="V70">
+        <v>7</v>
+      </c>
+      <c r="W70">
+        <v>7</v>
+      </c>
+      <c r="X70">
+        <v>8</v>
+      </c>
+      <c r="Y70">
+        <v>6</v>
+      </c>
+      <c r="Z70">
+        <v>9</v>
+      </c>
+      <c r="AA70">
+        <v>8</v>
+      </c>
+      <c r="AB70">
+        <v>6</v>
+      </c>
+      <c r="AC70">
+        <v>9</v>
+      </c>
+      <c r="AD70">
+        <v>6</v>
+      </c>
+      <c r="AE70">
+        <v>8</v>
+      </c>
+      <c r="AF70">
+        <v>4</v>
+      </c>
+      <c r="AG70">
+        <v>9</v>
+      </c>
+      <c r="AH70">
+        <v>6</v>
+      </c>
+      <c r="AI70">
+        <v>8</v>
+      </c>
+      <c r="AJ70">
+        <v>8</v>
+      </c>
+      <c r="AK70">
+        <v>8</v>
+      </c>
+      <c r="AL70">
+        <v>1</v>
+      </c>
+      <c r="AM70">
+        <v>7</v>
+      </c>
+      <c r="AN70">
+        <v>5</v>
+      </c>
+      <c r="AO70">
+        <v>1</v>
+      </c>
+      <c r="AP70">
+        <v>4</v>
+      </c>
+      <c r="AQ70">
+        <v>7</v>
+      </c>
+      <c r="AR70">
+        <v>4</v>
+      </c>
+      <c r="AS70">
+        <v>4</v>
+      </c>
+      <c r="AT70">
+        <v>10</v>
+      </c>
+      <c r="AU70">
+        <v>6</v>
+      </c>
+      <c r="AV70">
+        <v>5</v>
+      </c>
+      <c r="AW70">
+        <v>3</v>
+      </c>
+      <c r="AX70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A71" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B71" t="s">
+        <v>74</v>
+      </c>
+      <c r="C71">
+        <v>10</v>
+      </c>
+      <c r="D71">
+        <v>3</v>
+      </c>
+      <c r="E71">
+        <v>8</v>
+      </c>
+      <c r="F71">
+        <v>6</v>
+      </c>
+      <c r="G71">
+        <v>7</v>
+      </c>
+      <c r="H71">
+        <v>10</v>
+      </c>
+      <c r="I71">
+        <v>10</v>
+      </c>
+      <c r="J71">
+        <v>7</v>
+      </c>
+      <c r="K71">
+        <v>7</v>
+      </c>
+      <c r="L71">
+        <v>6</v>
+      </c>
+      <c r="M71">
+        <v>10</v>
+      </c>
+      <c r="N71">
+        <v>4</v>
+      </c>
+      <c r="O71">
+        <v>9</v>
+      </c>
+      <c r="P71">
+        <v>10</v>
+      </c>
+      <c r="Q71">
+        <v>6</v>
+      </c>
+      <c r="R71">
+        <v>3</v>
+      </c>
+      <c r="S71">
+        <v>2</v>
+      </c>
+      <c r="T71">
+        <v>7</v>
+      </c>
+      <c r="U71">
+        <v>5</v>
+      </c>
+      <c r="V71">
+        <v>10</v>
+      </c>
+      <c r="W71">
+        <v>1</v>
+      </c>
+      <c r="X71">
+        <v>9</v>
+      </c>
+      <c r="Y71">
+        <v>2</v>
+      </c>
+      <c r="Z71">
+        <v>1</v>
+      </c>
+      <c r="AA71">
+        <v>1</v>
+      </c>
+      <c r="AB71">
+        <v>3</v>
+      </c>
+      <c r="AC71">
+        <v>6</v>
+      </c>
+      <c r="AD71">
+        <v>5</v>
+      </c>
+      <c r="AE71">
+        <v>7</v>
+      </c>
+      <c r="AF71">
+        <v>5</v>
+      </c>
+      <c r="AG71">
+        <v>4</v>
+      </c>
+      <c r="AH71">
+        <v>3</v>
+      </c>
+      <c r="AI71">
+        <v>2</v>
+      </c>
+      <c r="AJ71">
+        <v>4</v>
+      </c>
+      <c r="AK71">
+        <v>9</v>
+      </c>
+      <c r="AL71">
+        <v>6</v>
+      </c>
+      <c r="AM71">
+        <v>4</v>
+      </c>
+      <c r="AN71">
+        <v>4</v>
+      </c>
+      <c r="AO71">
+        <v>8</v>
+      </c>
+      <c r="AP71">
+        <v>10</v>
+      </c>
+      <c r="AQ71">
+        <v>10</v>
+      </c>
+      <c r="AR71">
+        <v>8</v>
+      </c>
+      <c r="AS71">
+        <v>7</v>
+      </c>
+      <c r="AT71">
+        <v>9</v>
+      </c>
+      <c r="AU71">
+        <v>1</v>
+      </c>
+      <c r="AV71">
+        <v>3</v>
+      </c>
+      <c r="AW71">
+        <v>1</v>
+      </c>
+      <c r="AX71">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A72" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B72" t="s">
+        <v>74</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>6</v>
+      </c>
+      <c r="E72">
+        <v>10</v>
+      </c>
+      <c r="F72">
+        <v>7</v>
+      </c>
+      <c r="G72">
+        <v>6</v>
+      </c>
+      <c r="H72">
+        <v>10</v>
+      </c>
+      <c r="I72">
+        <v>10</v>
+      </c>
+      <c r="J72">
+        <v>9</v>
+      </c>
+      <c r="K72">
+        <v>3</v>
+      </c>
+      <c r="L72">
+        <v>2</v>
+      </c>
+      <c r="M72">
+        <v>6</v>
+      </c>
+      <c r="N72">
+        <v>10</v>
+      </c>
+      <c r="O72">
+        <v>2</v>
+      </c>
+      <c r="P72">
+        <v>1</v>
+      </c>
+      <c r="Q72">
+        <v>1</v>
+      </c>
+      <c r="R72">
+        <v>8</v>
+      </c>
+      <c r="S72">
+        <v>4</v>
+      </c>
+      <c r="T72">
+        <v>2</v>
+      </c>
+      <c r="U72">
+        <v>8</v>
+      </c>
+      <c r="V72">
+        <v>7</v>
+      </c>
+      <c r="W72">
+        <v>10</v>
+      </c>
+      <c r="X72">
+        <v>4</v>
+      </c>
+      <c r="Y72">
+        <v>6</v>
+      </c>
+      <c r="Z72">
+        <v>6</v>
+      </c>
+      <c r="AA72">
+        <v>2</v>
+      </c>
+      <c r="AB72">
+        <v>9</v>
+      </c>
+      <c r="AC72">
+        <v>6</v>
+      </c>
+      <c r="AD72">
+        <v>10</v>
+      </c>
+      <c r="AE72">
+        <v>6</v>
+      </c>
+      <c r="AF72">
+        <v>10</v>
+      </c>
+      <c r="AG72">
+        <v>4</v>
+      </c>
+      <c r="AH72">
+        <v>8</v>
+      </c>
+      <c r="AI72">
+        <v>1</v>
+      </c>
+      <c r="AJ72">
+        <v>6</v>
+      </c>
+      <c r="AK72">
+        <v>2</v>
+      </c>
+      <c r="AL72">
+        <v>8</v>
+      </c>
+      <c r="AM72">
+        <v>6</v>
+      </c>
+      <c r="AN72">
+        <v>1</v>
+      </c>
+      <c r="AO72">
+        <v>4</v>
+      </c>
+      <c r="AP72">
+        <v>3</v>
+      </c>
+      <c r="AQ72">
+        <v>8</v>
+      </c>
+      <c r="AR72">
+        <v>4</v>
+      </c>
+      <c r="AS72">
+        <v>4</v>
+      </c>
+      <c r="AT72">
+        <v>1</v>
+      </c>
+      <c r="AU72">
+        <v>1</v>
+      </c>
+      <c r="AV72">
+        <v>8</v>
+      </c>
+      <c r="AW72">
+        <v>4</v>
+      </c>
+      <c r="AX72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A73" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B73" t="s">
+        <v>74</v>
+      </c>
+      <c r="C73">
+        <v>10</v>
+      </c>
+      <c r="D73">
+        <v>10</v>
+      </c>
+      <c r="E73">
+        <v>10</v>
+      </c>
+      <c r="F73">
+        <v>4</v>
+      </c>
+      <c r="G73">
+        <v>9</v>
+      </c>
+      <c r="H73">
+        <v>3</v>
+      </c>
+      <c r="I73">
+        <v>9</v>
+      </c>
+      <c r="J73">
+        <v>6</v>
+      </c>
+      <c r="K73">
+        <v>9</v>
+      </c>
+      <c r="L73">
+        <v>8</v>
+      </c>
+      <c r="M73">
+        <v>10</v>
+      </c>
+      <c r="N73">
+        <v>1</v>
+      </c>
+      <c r="O73">
+        <v>2</v>
+      </c>
+      <c r="P73">
+        <v>6</v>
+      </c>
+      <c r="Q73">
+        <v>2</v>
+      </c>
+      <c r="R73">
+        <v>4</v>
+      </c>
+      <c r="S73">
+        <v>1</v>
+      </c>
+      <c r="T73">
+        <v>10</v>
+      </c>
+      <c r="U73">
+        <v>8</v>
+      </c>
+      <c r="V73">
+        <v>7</v>
+      </c>
+      <c r="W73">
+        <v>9</v>
+      </c>
+      <c r="X73">
+        <v>1</v>
+      </c>
+      <c r="Y73">
+        <v>8</v>
+      </c>
+      <c r="Z73">
+        <v>2</v>
+      </c>
+      <c r="AA73">
+        <v>1</v>
+      </c>
+      <c r="AB73">
+        <v>10</v>
+      </c>
+      <c r="AC73">
+        <v>8</v>
+      </c>
+      <c r="AD73">
+        <v>10</v>
+      </c>
+      <c r="AE73">
+        <v>8</v>
+      </c>
+      <c r="AF73">
+        <v>2</v>
+      </c>
+      <c r="AG73">
+        <v>10</v>
+      </c>
+      <c r="AH73">
+        <v>1</v>
+      </c>
+      <c r="AI73">
+        <v>6</v>
+      </c>
+      <c r="AJ73">
+        <v>1</v>
+      </c>
+      <c r="AK73">
+        <v>5</v>
+      </c>
+      <c r="AL73">
+        <v>9</v>
+      </c>
+      <c r="AM73">
+        <v>1</v>
+      </c>
+      <c r="AN73">
+        <v>1</v>
+      </c>
+      <c r="AO73">
+        <v>3</v>
+      </c>
+      <c r="AP73">
+        <v>3</v>
+      </c>
+      <c r="AQ73">
+        <v>8</v>
+      </c>
+      <c r="AR73">
+        <v>2</v>
+      </c>
+      <c r="AS73">
+        <v>2</v>
+      </c>
+      <c r="AT73">
+        <v>4</v>
+      </c>
+      <c r="AU73">
+        <v>6</v>
+      </c>
+      <c r="AV73">
+        <v>3</v>
+      </c>
+      <c r="AW73">
+        <v>2</v>
+      </c>
+      <c r="AX73">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A74" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B74" t="s">
+        <v>74</v>
+      </c>
+      <c r="C74">
+        <v>7</v>
+      </c>
+      <c r="D74">
+        <v>7</v>
+      </c>
+      <c r="E74">
+        <v>10</v>
+      </c>
+      <c r="F74">
+        <v>4</v>
+      </c>
+      <c r="G74">
+        <v>5</v>
+      </c>
+      <c r="H74">
+        <v>4</v>
+      </c>
+      <c r="I74">
+        <v>6</v>
+      </c>
+      <c r="J74">
+        <v>7</v>
+      </c>
+      <c r="K74">
+        <v>5</v>
+      </c>
+      <c r="L74">
+        <v>5</v>
+      </c>
+      <c r="M74">
+        <v>7</v>
+      </c>
+      <c r="N74">
+        <v>9</v>
+      </c>
+      <c r="O74">
+        <v>3</v>
+      </c>
+      <c r="P74">
+        <v>10</v>
+      </c>
+      <c r="Q74">
+        <v>5</v>
+      </c>
+      <c r="R74">
+        <v>6</v>
+      </c>
+      <c r="S74">
+        <v>6</v>
+      </c>
+      <c r="T74">
+        <v>1</v>
+      </c>
+      <c r="U74">
+        <v>6</v>
+      </c>
+      <c r="V74">
+        <v>2</v>
+      </c>
+      <c r="W74">
+        <v>1</v>
+      </c>
+      <c r="X74">
+        <v>2</v>
+      </c>
+      <c r="Y74">
+        <v>10</v>
+      </c>
+      <c r="Z74">
+        <v>8</v>
+      </c>
+      <c r="AA74">
+        <v>5</v>
+      </c>
+      <c r="AB74">
+        <v>1</v>
+      </c>
+      <c r="AC74">
+        <v>2</v>
+      </c>
+      <c r="AD74">
+        <v>4</v>
+      </c>
+      <c r="AE74">
+        <v>2</v>
+      </c>
+      <c r="AF74">
+        <v>1</v>
+      </c>
+      <c r="AG74">
+        <v>8</v>
+      </c>
+      <c r="AH74">
+        <v>9</v>
+      </c>
+      <c r="AI74">
+        <v>7</v>
+      </c>
+      <c r="AJ74">
+        <v>9</v>
+      </c>
+      <c r="AK74">
+        <v>2</v>
+      </c>
+      <c r="AL74">
+        <v>2</v>
+      </c>
+      <c r="AM74">
+        <v>10</v>
+      </c>
+      <c r="AN74">
+        <v>2</v>
+      </c>
+      <c r="AO74">
+        <v>6</v>
+      </c>
+      <c r="AP74">
+        <v>3</v>
+      </c>
+      <c r="AQ74">
+        <v>6</v>
+      </c>
+      <c r="AR74">
+        <v>8</v>
+      </c>
+      <c r="AS74">
+        <v>7</v>
+      </c>
+      <c r="AT74">
+        <v>2</v>
+      </c>
+      <c r="AU74">
+        <v>2</v>
+      </c>
+      <c r="AV74">
+        <v>2</v>
+      </c>
+      <c r="AW74">
+        <v>3</v>
+      </c>
+      <c r="AX74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A75" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B75" t="s">
+        <v>74</v>
+      </c>
+      <c r="C75">
+        <v>5</v>
+      </c>
+      <c r="D75">
+        <v>6</v>
+      </c>
+      <c r="E75">
+        <v>6</v>
+      </c>
+      <c r="F75">
+        <v>8</v>
+      </c>
+      <c r="G75">
+        <v>4</v>
+      </c>
+      <c r="H75">
+        <v>3</v>
+      </c>
+      <c r="I75">
+        <v>9</v>
+      </c>
+      <c r="J75">
+        <v>5</v>
+      </c>
+      <c r="K75">
+        <v>7</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="M75">
+        <v>9</v>
+      </c>
+      <c r="N75">
+        <v>5</v>
+      </c>
+      <c r="O75">
+        <v>8</v>
+      </c>
+      <c r="P75">
+        <v>1</v>
+      </c>
+      <c r="Q75">
+        <v>4</v>
+      </c>
+      <c r="R75">
+        <v>2</v>
+      </c>
+      <c r="S75">
+        <v>4</v>
+      </c>
+      <c r="T75">
+        <v>5</v>
+      </c>
+      <c r="U75">
+        <v>7</v>
+      </c>
+      <c r="V75">
+        <v>9</v>
+      </c>
+      <c r="W75">
+        <v>10</v>
+      </c>
+      <c r="X75">
+        <v>1</v>
+      </c>
+      <c r="Y75">
+        <v>9</v>
+      </c>
+      <c r="Z75">
+        <v>5</v>
+      </c>
+      <c r="AA75">
+        <v>4</v>
+      </c>
+      <c r="AB75">
+        <v>5</v>
+      </c>
+      <c r="AC75">
+        <v>10</v>
+      </c>
+      <c r="AD75">
+        <v>4</v>
+      </c>
+      <c r="AE75">
+        <v>2</v>
+      </c>
+      <c r="AF75">
+        <v>10</v>
+      </c>
+      <c r="AG75">
+        <v>4</v>
+      </c>
+      <c r="AH75">
+        <v>2</v>
+      </c>
+      <c r="AI75">
+        <v>2</v>
+      </c>
+      <c r="AJ75">
+        <v>5</v>
+      </c>
+      <c r="AK75">
+        <v>6</v>
+      </c>
+      <c r="AL75">
+        <v>5</v>
+      </c>
+      <c r="AM75">
+        <v>4</v>
+      </c>
+      <c r="AN75">
+        <v>6</v>
+      </c>
+      <c r="AO75">
+        <v>8</v>
+      </c>
+      <c r="AP75">
+        <v>2</v>
+      </c>
+      <c r="AQ75">
+        <v>7</v>
+      </c>
+      <c r="AR75">
+        <v>2</v>
+      </c>
+      <c r="AS75">
+        <v>3</v>
+      </c>
+      <c r="AT75">
+        <v>9</v>
+      </c>
+      <c r="AU75">
+        <v>5</v>
+      </c>
+      <c r="AV75">
+        <v>6</v>
+      </c>
+      <c r="AW75">
+        <v>3</v>
+      </c>
+      <c r="AX75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A76" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B76" t="s">
+        <v>74</v>
+      </c>
+      <c r="C76">
+        <v>7</v>
+      </c>
+      <c r="D76">
+        <v>7</v>
+      </c>
+      <c r="E76">
+        <v>3</v>
+      </c>
+      <c r="F76">
+        <v>6</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>7</v>
+      </c>
+      <c r="I76">
+        <v>3</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76">
+        <v>9</v>
+      </c>
+      <c r="L76">
+        <v>6</v>
+      </c>
+      <c r="M76">
+        <v>4</v>
+      </c>
+      <c r="N76">
+        <v>7</v>
+      </c>
+      <c r="O76">
+        <v>8</v>
+      </c>
+      <c r="P76">
+        <v>1</v>
+      </c>
+      <c r="Q76">
+        <v>4</v>
+      </c>
+      <c r="R76">
+        <v>2</v>
+      </c>
+      <c r="S76">
+        <v>6</v>
+      </c>
+      <c r="T76">
+        <v>8</v>
+      </c>
+      <c r="U76">
+        <v>1</v>
+      </c>
+      <c r="V76">
+        <v>2</v>
+      </c>
+      <c r="W76">
+        <v>8</v>
+      </c>
+      <c r="X76">
+        <v>7</v>
+      </c>
+      <c r="Y76">
+        <v>8</v>
+      </c>
+      <c r="Z76">
+        <v>10</v>
+      </c>
+      <c r="AA76">
+        <v>4</v>
+      </c>
+      <c r="AB76">
+        <v>6</v>
+      </c>
+      <c r="AC76">
+        <v>9</v>
+      </c>
+      <c r="AD76">
+        <v>3</v>
+      </c>
+      <c r="AE76">
+        <v>1</v>
+      </c>
+      <c r="AF76">
+        <v>2</v>
+      </c>
+      <c r="AG76">
+        <v>7</v>
+      </c>
+      <c r="AH76">
+        <v>5</v>
+      </c>
+      <c r="AI76">
+        <v>7</v>
+      </c>
+      <c r="AJ76">
+        <v>10</v>
+      </c>
+      <c r="AK76">
+        <v>2</v>
+      </c>
+      <c r="AL76">
+        <v>1</v>
+      </c>
+      <c r="AM76">
+        <v>8</v>
+      </c>
+      <c r="AN76">
+        <v>5</v>
+      </c>
+      <c r="AO76">
+        <v>2</v>
+      </c>
+      <c r="AP76">
+        <v>2</v>
+      </c>
+      <c r="AQ76">
+        <v>3</v>
+      </c>
+      <c r="AR76">
+        <v>7</v>
+      </c>
+      <c r="AS76">
+        <v>8</v>
+      </c>
+      <c r="AT76">
+        <v>2</v>
+      </c>
+      <c r="AU76">
+        <v>1</v>
+      </c>
+      <c r="AV76">
+        <v>2</v>
+      </c>
+      <c r="AW76">
+        <v>9</v>
+      </c>
+      <c r="AX76">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A77" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B77" t="s">
+        <v>74</v>
+      </c>
+      <c r="C77">
+        <v>9</v>
+      </c>
+      <c r="D77">
+        <v>9</v>
+      </c>
+      <c r="E77">
+        <v>5</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>5</v>
+      </c>
+      <c r="I77">
+        <v>9</v>
+      </c>
+      <c r="J77">
+        <v>3</v>
+      </c>
+      <c r="K77">
+        <v>10</v>
+      </c>
+      <c r="L77">
+        <v>2</v>
+      </c>
+      <c r="M77">
+        <v>10</v>
+      </c>
+      <c r="N77">
+        <v>7</v>
+      </c>
+      <c r="O77">
+        <v>6</v>
+      </c>
+      <c r="P77">
+        <v>1</v>
+      </c>
+      <c r="Q77">
+        <v>6</v>
+      </c>
+      <c r="R77">
+        <v>9</v>
+      </c>
+      <c r="S77">
+        <v>3</v>
+      </c>
+      <c r="T77">
+        <v>4</v>
+      </c>
+      <c r="U77">
+        <v>8</v>
+      </c>
+      <c r="V77">
+        <v>9</v>
+      </c>
+      <c r="W77">
+        <v>6</v>
+      </c>
+      <c r="X77">
+        <v>3</v>
+      </c>
+      <c r="Y77">
+        <v>5</v>
+      </c>
+      <c r="Z77">
+        <v>6</v>
+      </c>
+      <c r="AA77">
+        <v>8</v>
+      </c>
+      <c r="AB77">
+        <v>9</v>
+      </c>
+      <c r="AC77">
+        <v>7</v>
+      </c>
+      <c r="AD77">
+        <v>5</v>
+      </c>
+      <c r="AE77">
+        <v>3</v>
+      </c>
+      <c r="AF77">
+        <v>8</v>
+      </c>
+      <c r="AG77">
+        <v>5</v>
+      </c>
+      <c r="AH77">
+        <v>10</v>
+      </c>
+      <c r="AI77">
+        <v>5</v>
+      </c>
+      <c r="AJ77">
+        <v>2</v>
+      </c>
+      <c r="AK77">
+        <v>1</v>
+      </c>
+      <c r="AL77">
+        <v>10</v>
+      </c>
+      <c r="AM77">
+        <v>2</v>
+      </c>
+      <c r="AN77">
+        <v>4</v>
+      </c>
+      <c r="AO77">
+        <v>9</v>
+      </c>
+      <c r="AP77">
+        <v>4</v>
+      </c>
+      <c r="AQ77">
+        <v>10</v>
+      </c>
+      <c r="AR77">
+        <v>3</v>
+      </c>
+      <c r="AS77">
+        <v>10</v>
+      </c>
+      <c r="AT77">
+        <v>10</v>
+      </c>
+      <c r="AU77">
+        <v>5</v>
+      </c>
+      <c r="AV77">
+        <v>6</v>
+      </c>
+      <c r="AW77">
+        <v>10</v>
+      </c>
+      <c r="AX77">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A78" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B78" t="s">
+        <v>74</v>
+      </c>
+      <c r="C78">
+        <v>9</v>
+      </c>
+      <c r="D78">
+        <v>9</v>
+      </c>
+      <c r="E78">
+        <v>4</v>
+      </c>
+      <c r="F78">
+        <v>5</v>
+      </c>
+      <c r="G78">
+        <v>5</v>
+      </c>
+      <c r="H78">
+        <v>4</v>
+      </c>
+      <c r="I78">
+        <v>2</v>
+      </c>
+      <c r="J78">
+        <v>9</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="L78">
+        <v>9</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+      <c r="N78">
+        <v>4</v>
+      </c>
+      <c r="O78">
+        <v>4</v>
+      </c>
+      <c r="P78">
+        <v>1</v>
+      </c>
+      <c r="Q78">
+        <v>10</v>
+      </c>
+      <c r="R78">
+        <v>3</v>
+      </c>
+      <c r="S78">
+        <v>3</v>
+      </c>
+      <c r="T78">
+        <v>4</v>
+      </c>
+      <c r="U78">
+        <v>10</v>
+      </c>
+      <c r="V78">
+        <v>3</v>
+      </c>
+      <c r="W78">
+        <v>9</v>
+      </c>
+      <c r="X78">
+        <v>7</v>
+      </c>
+      <c r="Y78">
+        <v>1</v>
+      </c>
+      <c r="Z78">
+        <v>10</v>
+      </c>
+      <c r="AA78">
+        <v>10</v>
+      </c>
+      <c r="AB78">
+        <v>6</v>
+      </c>
+      <c r="AC78">
+        <v>9</v>
+      </c>
+      <c r="AD78">
+        <v>4</v>
+      </c>
+      <c r="AE78">
+        <v>9</v>
+      </c>
+      <c r="AF78">
+        <v>8</v>
+      </c>
+      <c r="AG78">
+        <v>9</v>
+      </c>
+      <c r="AH78">
+        <v>6</v>
+      </c>
+      <c r="AI78">
+        <v>1</v>
+      </c>
+      <c r="AJ78">
+        <v>6</v>
+      </c>
+      <c r="AK78">
+        <v>10</v>
+      </c>
+      <c r="AL78">
+        <v>5</v>
+      </c>
+      <c r="AM78">
+        <v>5</v>
+      </c>
+      <c r="AN78">
+        <v>5</v>
+      </c>
+      <c r="AO78">
+        <v>5</v>
+      </c>
+      <c r="AP78">
+        <v>7</v>
+      </c>
+      <c r="AQ78">
+        <v>4</v>
+      </c>
+      <c r="AR78">
+        <v>4</v>
+      </c>
+      <c r="AS78">
+        <v>2</v>
+      </c>
+      <c r="AT78">
+        <v>3</v>
+      </c>
+      <c r="AU78">
+        <v>5</v>
+      </c>
+      <c r="AV78">
+        <v>10</v>
+      </c>
+      <c r="AW78">
+        <v>1</v>
+      </c>
+      <c r="AX78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A79" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B79" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79">
+        <v>6</v>
+      </c>
+      <c r="D79">
+        <v>8</v>
+      </c>
+      <c r="E79">
+        <v>10</v>
+      </c>
+      <c r="F79">
+        <v>4</v>
+      </c>
+      <c r="G79">
+        <v>3</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>8</v>
+      </c>
+      <c r="J79">
+        <v>10</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>5</v>
+      </c>
+      <c r="M79">
+        <v>5</v>
+      </c>
+      <c r="N79">
+        <v>7</v>
+      </c>
+      <c r="O79">
+        <v>1</v>
+      </c>
+      <c r="P79">
+        <v>2</v>
+      </c>
+      <c r="Q79">
+        <v>9</v>
+      </c>
+      <c r="R79">
+        <v>7</v>
+      </c>
+      <c r="S79">
+        <v>2</v>
+      </c>
+      <c r="T79">
+        <v>7</v>
+      </c>
+      <c r="U79">
+        <v>6</v>
+      </c>
+      <c r="V79">
+        <v>4</v>
+      </c>
+      <c r="W79">
+        <v>1</v>
+      </c>
+      <c r="X79">
+        <v>9</v>
+      </c>
+      <c r="Y79">
+        <v>7</v>
+      </c>
+      <c r="Z79">
+        <v>5</v>
+      </c>
+      <c r="AA79">
+        <v>6</v>
+      </c>
+      <c r="AB79">
+        <v>3</v>
+      </c>
+      <c r="AC79">
+        <v>8</v>
+      </c>
+      <c r="AD79">
+        <v>10</v>
+      </c>
+      <c r="AE79">
+        <v>5</v>
+      </c>
+      <c r="AF79">
+        <v>3</v>
+      </c>
+      <c r="AG79">
+        <v>3</v>
+      </c>
+      <c r="AH79">
+        <v>9</v>
+      </c>
+      <c r="AI79">
+        <v>2</v>
+      </c>
+      <c r="AJ79">
+        <v>8</v>
+      </c>
+      <c r="AK79">
+        <v>1</v>
+      </c>
+      <c r="AL79">
+        <v>1</v>
+      </c>
+      <c r="AM79">
+        <v>3</v>
+      </c>
+      <c r="AN79">
+        <v>8</v>
+      </c>
+      <c r="AO79">
+        <v>2</v>
+      </c>
+      <c r="AP79">
+        <v>9</v>
+      </c>
+      <c r="AQ79">
+        <v>1</v>
+      </c>
+      <c r="AR79">
+        <v>7</v>
+      </c>
+      <c r="AS79">
+        <v>4</v>
+      </c>
+      <c r="AT79">
+        <v>9</v>
+      </c>
+      <c r="AU79">
+        <v>4</v>
+      </c>
+      <c r="AV79">
+        <v>9</v>
+      </c>
+      <c r="AW79">
+        <v>7</v>
+      </c>
+      <c r="AX79">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A80" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B80" t="s">
+        <v>74</v>
+      </c>
+      <c r="C80">
+        <v>3</v>
+      </c>
+      <c r="D80">
+        <v>8</v>
+      </c>
+      <c r="E80">
+        <v>5</v>
+      </c>
+      <c r="F80">
+        <v>8</v>
+      </c>
+      <c r="G80">
+        <v>6</v>
+      </c>
+      <c r="H80">
+        <v>6</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80">
+        <v>1</v>
+      </c>
+      <c r="K80">
+        <v>6</v>
+      </c>
+      <c r="L80">
+        <v>7</v>
+      </c>
+      <c r="M80">
+        <v>9</v>
+      </c>
+      <c r="N80">
+        <v>8</v>
+      </c>
+      <c r="O80">
+        <v>5</v>
+      </c>
+      <c r="P80">
+        <v>1</v>
+      </c>
+      <c r="Q80">
+        <v>4</v>
+      </c>
+      <c r="R80">
+        <v>6</v>
+      </c>
+      <c r="S80">
+        <v>5</v>
+      </c>
+      <c r="T80">
+        <v>8</v>
+      </c>
+      <c r="U80">
+        <v>10</v>
+      </c>
+      <c r="V80">
+        <v>2</v>
+      </c>
+      <c r="W80">
+        <v>5</v>
+      </c>
+      <c r="X80">
+        <v>8</v>
+      </c>
+      <c r="Y80">
+        <v>5</v>
+      </c>
+      <c r="Z80">
+        <v>5</v>
+      </c>
+      <c r="AA80">
+        <v>6</v>
+      </c>
+      <c r="AB80">
+        <v>9</v>
+      </c>
+      <c r="AC80">
+        <v>9</v>
+      </c>
+      <c r="AD80">
+        <v>10</v>
+      </c>
+      <c r="AE80">
+        <v>4</v>
+      </c>
+      <c r="AF80">
+        <v>7</v>
+      </c>
+      <c r="AG80">
+        <v>6</v>
+      </c>
+      <c r="AH80">
+        <v>5</v>
+      </c>
+      <c r="AI80">
+        <v>10</v>
+      </c>
+      <c r="AJ80">
+        <v>4</v>
+      </c>
+      <c r="AK80">
+        <v>9</v>
+      </c>
+      <c r="AL80">
+        <v>8</v>
+      </c>
+      <c r="AM80">
+        <v>6</v>
+      </c>
+      <c r="AN80">
+        <v>3</v>
+      </c>
+      <c r="AO80">
+        <v>3</v>
+      </c>
+      <c r="AP80">
+        <v>2</v>
+      </c>
+      <c r="AQ80">
+        <v>4</v>
+      </c>
+      <c r="AR80">
+        <v>8</v>
+      </c>
+      <c r="AS80">
+        <v>2</v>
+      </c>
+      <c r="AT80">
+        <v>2</v>
+      </c>
+      <c r="AU80">
+        <v>4</v>
+      </c>
+      <c r="AV80">
+        <v>8</v>
+      </c>
+      <c r="AW80">
+        <v>1</v>
+      </c>
+      <c r="AX80">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A81" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B81" t="s">
+        <v>74</v>
+      </c>
+      <c r="C81">
+        <v>10</v>
+      </c>
+      <c r="D81">
+        <v>9</v>
+      </c>
+      <c r="E81">
+        <v>9</v>
+      </c>
+      <c r="F81">
+        <v>6</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+      <c r="H81">
+        <v>5</v>
+      </c>
+      <c r="I81">
+        <v>5</v>
+      </c>
+      <c r="J81">
+        <v>2</v>
+      </c>
+      <c r="K81">
+        <v>3</v>
+      </c>
+      <c r="L81">
+        <v>7</v>
+      </c>
+      <c r="M81">
+        <v>5</v>
+      </c>
+      <c r="N81">
+        <v>2</v>
+      </c>
+      <c r="O81">
+        <v>4</v>
+      </c>
+      <c r="P81">
+        <v>3</v>
+      </c>
+      <c r="Q81">
+        <v>6</v>
+      </c>
+      <c r="R81">
+        <v>4</v>
+      </c>
+      <c r="S81">
+        <v>7</v>
+      </c>
+      <c r="T81">
+        <v>9</v>
+      </c>
+      <c r="U81">
+        <v>9</v>
+      </c>
+      <c r="V81">
+        <v>3</v>
+      </c>
+      <c r="W81">
+        <v>5</v>
+      </c>
+      <c r="X81">
+        <v>10</v>
+      </c>
+      <c r="Y81">
+        <v>8</v>
+      </c>
+      <c r="Z81">
+        <v>7</v>
+      </c>
+      <c r="AA81">
+        <v>8</v>
+      </c>
+      <c r="AB81">
+        <v>6</v>
+      </c>
+      <c r="AC81">
+        <v>4</v>
+      </c>
+      <c r="AD81">
+        <v>4</v>
+      </c>
+      <c r="AE81">
+        <v>8</v>
+      </c>
+      <c r="AF81">
+        <v>1</v>
+      </c>
+      <c r="AG81">
+        <v>9</v>
+      </c>
+      <c r="AH81">
+        <v>4</v>
+      </c>
+      <c r="AI81">
+        <v>5</v>
+      </c>
+      <c r="AJ81">
+        <v>5</v>
+      </c>
+      <c r="AK81">
+        <v>1</v>
+      </c>
+      <c r="AL81">
+        <v>1</v>
+      </c>
+      <c r="AM81">
+        <v>7</v>
+      </c>
+      <c r="AN81">
+        <v>9</v>
+      </c>
+      <c r="AO81">
+        <v>9</v>
+      </c>
+      <c r="AP81">
+        <v>7</v>
+      </c>
+      <c r="AQ81">
+        <v>10</v>
+      </c>
+      <c r="AR81">
+        <v>7</v>
+      </c>
+      <c r="AS81">
+        <v>9</v>
+      </c>
+      <c r="AT81">
+        <v>5</v>
+      </c>
+      <c r="AU81">
+        <v>4</v>
+      </c>
+      <c r="AV81">
+        <v>10</v>
+      </c>
+      <c r="AW81">
+        <v>10</v>
+      </c>
+      <c r="AX81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A82" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B82" t="s">
+        <v>74</v>
+      </c>
+      <c r="C82">
+        <v>10</v>
+      </c>
+      <c r="D82">
+        <v>5</v>
+      </c>
+      <c r="E82">
+        <v>7</v>
+      </c>
+      <c r="F82">
+        <v>6</v>
+      </c>
+      <c r="G82">
+        <v>7</v>
+      </c>
+      <c r="H82">
+        <v>7</v>
+      </c>
+      <c r="I82">
+        <v>7</v>
+      </c>
+      <c r="J82">
+        <v>5</v>
+      </c>
+      <c r="K82">
+        <v>4</v>
+      </c>
+      <c r="L82">
+        <v>3</v>
+      </c>
+      <c r="M82">
+        <v>5</v>
+      </c>
+      <c r="N82">
+        <v>1</v>
+      </c>
+      <c r="O82">
+        <v>2</v>
+      </c>
+      <c r="P82">
+        <v>6</v>
+      </c>
+      <c r="Q82">
+        <v>10</v>
+      </c>
+      <c r="R82">
+        <v>1</v>
+      </c>
+      <c r="S82">
+        <v>2</v>
+      </c>
+      <c r="T82">
+        <v>5</v>
+      </c>
+      <c r="U82">
+        <v>7</v>
+      </c>
+      <c r="V82">
+        <v>8</v>
+      </c>
+      <c r="W82">
+        <v>6</v>
+      </c>
+      <c r="X82">
+        <v>9</v>
+      </c>
+      <c r="Y82">
+        <v>5</v>
+      </c>
+      <c r="Z82">
+        <v>9</v>
+      </c>
+      <c r="AA82">
+        <v>5</v>
+      </c>
+      <c r="AB82">
+        <v>4</v>
+      </c>
+      <c r="AC82">
+        <v>6</v>
+      </c>
+      <c r="AD82">
+        <v>4</v>
+      </c>
+      <c r="AE82">
+        <v>8</v>
+      </c>
+      <c r="AF82">
+        <v>8</v>
+      </c>
+      <c r="AG82">
+        <v>6</v>
+      </c>
+      <c r="AH82">
+        <v>10</v>
+      </c>
+      <c r="AI82">
+        <v>8</v>
+      </c>
+      <c r="AJ82">
+        <v>4</v>
+      </c>
+      <c r="AK82">
+        <v>10</v>
+      </c>
+      <c r="AL82">
+        <v>2</v>
+      </c>
+      <c r="AM82">
+        <v>3</v>
+      </c>
+      <c r="AN82">
+        <v>6</v>
+      </c>
+      <c r="AO82">
+        <v>4</v>
+      </c>
+      <c r="AP82">
+        <v>3</v>
+      </c>
+      <c r="AQ82">
+        <v>8</v>
+      </c>
+      <c r="AR82">
+        <v>1</v>
+      </c>
+      <c r="AS82">
+        <v>7</v>
+      </c>
+      <c r="AT82">
+        <v>7</v>
+      </c>
+      <c r="AU82">
+        <v>10</v>
+      </c>
+      <c r="AV82">
+        <v>4</v>
+      </c>
+      <c r="AW82">
+        <v>8</v>
+      </c>
+      <c r="AX82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A83" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B83" t="s">
+        <v>74</v>
+      </c>
+      <c r="C83">
+        <v>9</v>
+      </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
+      <c r="E83">
+        <v>8</v>
+      </c>
+      <c r="F83">
+        <v>8</v>
+      </c>
+      <c r="G83">
+        <v>4</v>
+      </c>
+      <c r="H83">
+        <v>6</v>
+      </c>
+      <c r="I83">
+        <v>9</v>
+      </c>
+      <c r="J83">
+        <v>2</v>
+      </c>
+      <c r="K83">
+        <v>9</v>
+      </c>
+      <c r="L83">
+        <v>8</v>
+      </c>
+      <c r="M83">
+        <v>10</v>
+      </c>
+      <c r="N83">
+        <v>5</v>
+      </c>
+      <c r="O83">
+        <v>4</v>
+      </c>
+      <c r="P83">
+        <v>2</v>
+      </c>
+      <c r="Q83">
+        <v>8</v>
+      </c>
+      <c r="R83">
+        <v>1</v>
+      </c>
+      <c r="S83">
+        <v>7</v>
+      </c>
+      <c r="T83">
+        <v>6</v>
+      </c>
+      <c r="U83">
+        <v>9</v>
+      </c>
+      <c r="V83">
+        <v>6</v>
+      </c>
+      <c r="W83">
+        <v>3</v>
+      </c>
+      <c r="X83">
+        <v>5</v>
+      </c>
+      <c r="Y83">
+        <v>7</v>
+      </c>
+      <c r="Z83">
+        <v>7</v>
+      </c>
+      <c r="AA83">
+        <v>7</v>
+      </c>
+      <c r="AB83">
+        <v>10</v>
+      </c>
+      <c r="AC83">
+        <v>5</v>
+      </c>
+      <c r="AD83">
+        <v>9</v>
+      </c>
+      <c r="AE83">
+        <v>7</v>
+      </c>
+      <c r="AF83">
+        <v>5</v>
+      </c>
+      <c r="AG83">
+        <v>10</v>
+      </c>
+      <c r="AH83">
+        <v>3</v>
+      </c>
+      <c r="AI83">
+        <v>10</v>
+      </c>
+      <c r="AJ83">
+        <v>6</v>
+      </c>
+      <c r="AK83">
+        <v>7</v>
+      </c>
+      <c r="AL83">
+        <v>1</v>
+      </c>
+      <c r="AM83">
+        <v>9</v>
+      </c>
+      <c r="AN83">
+        <v>5</v>
+      </c>
+      <c r="AO83">
+        <v>5</v>
+      </c>
+      <c r="AP83">
+        <v>5</v>
+      </c>
+      <c r="AQ83">
+        <v>4</v>
+      </c>
+      <c r="AR83">
+        <v>10</v>
+      </c>
+      <c r="AS83">
+        <v>5</v>
+      </c>
+      <c r="AT83">
+        <v>8</v>
+      </c>
+      <c r="AU83">
+        <v>1</v>
+      </c>
+      <c r="AV83">
+        <v>6</v>
+      </c>
+      <c r="AW83">
+        <v>2</v>
+      </c>
+      <c r="AX83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A84" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B84" t="s">
+        <v>74</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84">
+        <v>3</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="F84">
+        <v>6</v>
+      </c>
+      <c r="G84">
+        <v>7</v>
+      </c>
+      <c r="H84">
+        <v>9</v>
+      </c>
+      <c r="I84">
+        <v>10</v>
+      </c>
+      <c r="J84">
+        <v>6</v>
+      </c>
+      <c r="K84">
+        <v>10</v>
+      </c>
+      <c r="L84">
+        <v>2</v>
+      </c>
+      <c r="M84">
+        <v>2</v>
+      </c>
+      <c r="N84">
+        <v>8</v>
+      </c>
+      <c r="O84">
+        <v>7</v>
+      </c>
+      <c r="P84">
+        <v>8</v>
+      </c>
+      <c r="Q84">
+        <v>6</v>
+      </c>
+      <c r="R84">
+        <v>6</v>
+      </c>
+      <c r="S84">
+        <v>2</v>
+      </c>
+      <c r="T84">
+        <v>3</v>
+      </c>
+      <c r="U84">
+        <v>6</v>
+      </c>
+      <c r="V84">
+        <v>9</v>
+      </c>
+      <c r="W84">
+        <v>2</v>
+      </c>
+      <c r="X84">
+        <v>3</v>
+      </c>
+      <c r="Y84">
+        <v>8</v>
+      </c>
+      <c r="Z84">
+        <v>4</v>
+      </c>
+      <c r="AA84">
+        <v>5</v>
+      </c>
+      <c r="AB84">
+        <v>4</v>
+      </c>
+      <c r="AC84">
+        <v>3</v>
+      </c>
+      <c r="AD84">
+        <v>10</v>
+      </c>
+      <c r="AE84">
+        <v>5</v>
+      </c>
+      <c r="AF84">
+        <v>9</v>
+      </c>
+      <c r="AG84">
+        <v>1</v>
+      </c>
+      <c r="AH84">
+        <v>10</v>
+      </c>
+      <c r="AI84">
+        <v>9</v>
+      </c>
+      <c r="AJ84">
+        <v>7</v>
+      </c>
+      <c r="AK84">
+        <v>6</v>
+      </c>
+      <c r="AL84">
+        <v>1</v>
+      </c>
+      <c r="AM84">
+        <v>5</v>
+      </c>
+      <c r="AN84">
+        <v>2</v>
+      </c>
+      <c r="AO84">
+        <v>10</v>
+      </c>
+      <c r="AP84">
+        <v>4</v>
+      </c>
+      <c r="AQ84">
+        <v>5</v>
+      </c>
+      <c r="AR84">
+        <v>2</v>
+      </c>
+      <c r="AS84">
+        <v>7</v>
+      </c>
+      <c r="AT84">
+        <v>10</v>
+      </c>
+      <c r="AU84">
+        <v>4</v>
+      </c>
+      <c r="AV84">
+        <v>3</v>
+      </c>
+      <c r="AW84">
+        <v>6</v>
+      </c>
+      <c r="AX84">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A85" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B85" t="s">
+        <v>74</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+      <c r="D85">
+        <v>4</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85">
+        <v>6</v>
+      </c>
+      <c r="G85">
+        <v>6</v>
+      </c>
+      <c r="H85">
+        <v>7</v>
+      </c>
+      <c r="I85">
+        <v>8</v>
+      </c>
+      <c r="J85">
+        <v>3</v>
+      </c>
+      <c r="K85">
+        <v>6</v>
+      </c>
+      <c r="L85">
+        <v>9</v>
+      </c>
+      <c r="M85">
+        <v>7</v>
+      </c>
+      <c r="N85">
+        <v>1</v>
+      </c>
+      <c r="O85">
+        <v>1</v>
+      </c>
+      <c r="P85">
+        <v>9</v>
+      </c>
+      <c r="Q85">
+        <v>6</v>
+      </c>
+      <c r="R85">
+        <v>7</v>
+      </c>
+      <c r="S85">
+        <v>8</v>
+      </c>
+      <c r="T85">
+        <v>5</v>
+      </c>
+      <c r="U85">
+        <v>5</v>
+      </c>
+      <c r="V85">
+        <v>10</v>
+      </c>
+      <c r="W85">
+        <v>9</v>
+      </c>
+      <c r="X85">
+        <v>1</v>
+      </c>
+      <c r="Y85">
+        <v>3</v>
+      </c>
+      <c r="Z85">
+        <v>5</v>
+      </c>
+      <c r="AA85">
+        <v>8</v>
+      </c>
+      <c r="AB85">
+        <v>8</v>
+      </c>
+      <c r="AC85">
+        <v>2</v>
+      </c>
+      <c r="AD85">
+        <v>7</v>
+      </c>
+      <c r="AE85">
+        <v>8</v>
+      </c>
+      <c r="AF85">
+        <v>10</v>
+      </c>
+      <c r="AG85">
+        <v>5</v>
+      </c>
+      <c r="AH85">
+        <v>2</v>
+      </c>
+      <c r="AI85">
+        <v>1</v>
+      </c>
+      <c r="AJ85">
+        <v>9</v>
+      </c>
+      <c r="AK85">
+        <v>10</v>
+      </c>
+      <c r="AL85">
+        <v>7</v>
+      </c>
+      <c r="AM85">
+        <v>6</v>
+      </c>
+      <c r="AN85">
+        <v>1</v>
+      </c>
+      <c r="AO85">
+        <v>3</v>
+      </c>
+      <c r="AP85">
+        <v>5</v>
+      </c>
+      <c r="AQ85">
+        <v>9</v>
+      </c>
+      <c r="AR85">
+        <v>9</v>
+      </c>
+      <c r="AS85">
+        <v>3</v>
+      </c>
+      <c r="AT85">
+        <v>8</v>
+      </c>
+      <c r="AU85">
+        <v>2</v>
+      </c>
+      <c r="AV85">
+        <v>10</v>
+      </c>
+      <c r="AW85">
+        <v>3</v>
+      </c>
+      <c r="AX85">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A86" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B86" t="s">
+        <v>74</v>
+      </c>
+      <c r="C86">
+        <v>10</v>
+      </c>
+      <c r="D86">
+        <v>5</v>
+      </c>
+      <c r="E86">
+        <v>10</v>
+      </c>
+      <c r="F86">
+        <v>10</v>
+      </c>
+      <c r="G86">
+        <v>5</v>
+      </c>
+      <c r="H86">
+        <v>4</v>
+      </c>
+      <c r="I86">
+        <v>3</v>
+      </c>
+      <c r="J86">
+        <v>3</v>
+      </c>
+      <c r="K86">
+        <v>5</v>
+      </c>
+      <c r="L86">
+        <v>8</v>
+      </c>
+      <c r="M86">
+        <v>2</v>
+      </c>
+      <c r="N86">
+        <v>2</v>
+      </c>
+      <c r="O86">
+        <v>9</v>
+      </c>
+      <c r="P86">
+        <v>5</v>
+      </c>
+      <c r="Q86">
+        <v>2</v>
+      </c>
+      <c r="R86">
+        <v>1</v>
+      </c>
+      <c r="S86">
+        <v>5</v>
+      </c>
+      <c r="T86">
+        <v>3</v>
+      </c>
+      <c r="U86">
+        <v>1</v>
+      </c>
+      <c r="V86">
+        <v>9</v>
+      </c>
+      <c r="W86">
+        <v>9</v>
+      </c>
+      <c r="X86">
+        <v>4</v>
+      </c>
+      <c r="Y86">
+        <v>1</v>
+      </c>
+      <c r="Z86">
+        <v>10</v>
+      </c>
+      <c r="AA86">
+        <v>8</v>
+      </c>
+      <c r="AB86">
+        <v>8</v>
+      </c>
+      <c r="AC86">
+        <v>7</v>
+      </c>
+      <c r="AD86">
+        <v>5</v>
+      </c>
+      <c r="AE86">
+        <v>6</v>
+      </c>
+      <c r="AF86">
+        <v>8</v>
+      </c>
+      <c r="AG86">
+        <v>1</v>
+      </c>
+      <c r="AH86">
+        <v>5</v>
+      </c>
+      <c r="AI86">
+        <v>2</v>
+      </c>
+      <c r="AJ86">
+        <v>10</v>
+      </c>
+      <c r="AK86">
+        <v>10</v>
+      </c>
+      <c r="AL86">
+        <v>6</v>
+      </c>
+      <c r="AM86">
+        <v>8</v>
+      </c>
+      <c r="AN86">
+        <v>5</v>
+      </c>
+      <c r="AO86">
+        <v>9</v>
+      </c>
+      <c r="AP86">
+        <v>2</v>
+      </c>
+      <c r="AQ86">
+        <v>10</v>
+      </c>
+      <c r="AR86">
+        <v>8</v>
+      </c>
+      <c r="AS86">
+        <v>9</v>
+      </c>
+      <c r="AT86">
+        <v>1</v>
+      </c>
+      <c r="AU86">
+        <v>2</v>
+      </c>
+      <c r="AV86">
+        <v>2</v>
+      </c>
+      <c r="AW86">
+        <v>7</v>
+      </c>
+      <c r="AX86">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A87" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B87" t="s">
+        <v>74</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87">
+        <v>3</v>
+      </c>
+      <c r="E87">
+        <v>8</v>
+      </c>
+      <c r="F87">
+        <v>6</v>
+      </c>
+      <c r="G87">
+        <v>2</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>3</v>
+      </c>
+      <c r="J87">
+        <v>9</v>
+      </c>
+      <c r="K87">
+        <v>9</v>
+      </c>
+      <c r="L87">
+        <v>7</v>
+      </c>
+      <c r="M87">
+        <v>10</v>
+      </c>
+      <c r="N87">
+        <v>1</v>
+      </c>
+      <c r="O87">
+        <v>7</v>
+      </c>
+      <c r="P87">
+        <v>7</v>
+      </c>
+      <c r="Q87">
+        <v>8</v>
+      </c>
+      <c r="R87">
+        <v>7</v>
+      </c>
+      <c r="S87">
+        <v>5</v>
+      </c>
+      <c r="T87">
+        <v>1</v>
+      </c>
+      <c r="U87">
+        <v>3</v>
+      </c>
+      <c r="V87">
+        <v>8</v>
+      </c>
+      <c r="W87">
+        <v>1</v>
+      </c>
+      <c r="X87">
+        <v>5</v>
+      </c>
+      <c r="Y87">
+        <v>2</v>
+      </c>
+      <c r="Z87">
+        <v>6</v>
+      </c>
+      <c r="AA87">
+        <v>3</v>
+      </c>
+      <c r="AB87">
+        <v>3</v>
+      </c>
+      <c r="AC87">
+        <v>2</v>
+      </c>
+      <c r="AD87">
+        <v>5</v>
+      </c>
+      <c r="AE87">
+        <v>4</v>
+      </c>
+      <c r="AF87">
+        <v>5</v>
+      </c>
+      <c r="AG87">
+        <v>6</v>
+      </c>
+      <c r="AH87">
+        <v>6</v>
+      </c>
+      <c r="AI87">
+        <v>9</v>
+      </c>
+      <c r="AJ87">
+        <v>8</v>
+      </c>
+      <c r="AK87">
+        <v>6</v>
+      </c>
+      <c r="AL87">
+        <v>3</v>
+      </c>
+      <c r="AM87">
+        <v>5</v>
+      </c>
+      <c r="AN87">
+        <v>2</v>
+      </c>
+      <c r="AO87">
+        <v>2</v>
+      </c>
+      <c r="AP87">
+        <v>1</v>
+      </c>
+      <c r="AQ87">
+        <v>2</v>
+      </c>
+      <c r="AR87">
+        <v>1</v>
+      </c>
+      <c r="AS87">
+        <v>2</v>
+      </c>
+      <c r="AT87">
+        <v>3</v>
+      </c>
+      <c r="AU87">
+        <v>2</v>
+      </c>
+      <c r="AV87">
+        <v>10</v>
+      </c>
+      <c r="AW87">
+        <v>5</v>
+      </c>
+      <c r="AX87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A88" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B88" t="s">
+        <v>74</v>
+      </c>
+      <c r="C88">
+        <v>10</v>
+      </c>
+      <c r="D88">
+        <v>6</v>
+      </c>
+      <c r="E88">
+        <v>9</v>
+      </c>
+      <c r="F88">
+        <v>2</v>
+      </c>
+      <c r="G88">
+        <v>10</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <v>5</v>
+      </c>
+      <c r="J88">
+        <v>8</v>
+      </c>
+      <c r="K88">
+        <v>6</v>
+      </c>
+      <c r="L88">
+        <v>6</v>
+      </c>
+      <c r="M88">
+        <v>10</v>
+      </c>
+      <c r="N88">
+        <v>10</v>
+      </c>
+      <c r="O88">
+        <v>9</v>
+      </c>
+      <c r="P88">
+        <v>3</v>
+      </c>
+      <c r="Q88">
+        <v>10</v>
+      </c>
+      <c r="R88">
+        <v>3</v>
+      </c>
+      <c r="S88">
+        <v>6</v>
+      </c>
+      <c r="T88">
+        <v>8</v>
+      </c>
+      <c r="U88">
+        <v>7</v>
+      </c>
+      <c r="V88">
+        <v>7</v>
+      </c>
+      <c r="W88">
+        <v>4</v>
+      </c>
+      <c r="X88">
+        <v>6</v>
+      </c>
+      <c r="Y88">
+        <v>8</v>
+      </c>
+      <c r="Z88">
+        <v>3</v>
+      </c>
+      <c r="AA88">
+        <v>5</v>
+      </c>
+      <c r="AB88">
+        <v>2</v>
+      </c>
+      <c r="AC88">
+        <v>6</v>
+      </c>
+      <c r="AD88">
+        <v>3</v>
+      </c>
+      <c r="AE88">
+        <v>8</v>
+      </c>
+      <c r="AF88">
+        <v>6</v>
+      </c>
+      <c r="AG88">
+        <v>9</v>
+      </c>
+      <c r="AH88">
+        <v>7</v>
+      </c>
+      <c r="AI88">
+        <v>1</v>
+      </c>
+      <c r="AJ88">
+        <v>3</v>
+      </c>
+      <c r="AK88">
+        <v>7</v>
+      </c>
+      <c r="AL88">
+        <v>3</v>
+      </c>
+      <c r="AM88">
+        <v>6</v>
+      </c>
+      <c r="AN88">
+        <v>10</v>
+      </c>
+      <c r="AO88">
+        <v>10</v>
+      </c>
+      <c r="AP88">
+        <v>4</v>
+      </c>
+      <c r="AQ88">
+        <v>2</v>
+      </c>
+      <c r="AR88">
+        <v>9</v>
+      </c>
+      <c r="AS88">
+        <v>1</v>
+      </c>
+      <c r="AT88">
+        <v>7</v>
+      </c>
+      <c r="AU88">
+        <v>7</v>
+      </c>
+      <c r="AV88">
+        <v>2</v>
+      </c>
+      <c r="AW88">
+        <v>7</v>
+      </c>
+      <c r="AX88">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A89" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B89" t="s">
+        <v>74</v>
+      </c>
+      <c r="C89">
+        <v>10</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>6</v>
+      </c>
+      <c r="F89">
+        <v>3</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>4</v>
+      </c>
+      <c r="I89">
+        <v>5</v>
+      </c>
+      <c r="J89">
+        <v>4</v>
+      </c>
+      <c r="K89">
+        <v>6</v>
+      </c>
+      <c r="L89">
+        <v>2</v>
+      </c>
+      <c r="M89">
+        <v>10</v>
+      </c>
+      <c r="N89">
+        <v>2</v>
+      </c>
+      <c r="O89">
+        <v>8</v>
+      </c>
+      <c r="P89">
+        <v>10</v>
+      </c>
+      <c r="Q89">
+        <v>9</v>
+      </c>
+      <c r="R89">
+        <v>4</v>
+      </c>
+      <c r="S89">
+        <v>7</v>
+      </c>
+      <c r="T89">
+        <v>10</v>
+      </c>
+      <c r="U89">
+        <v>2</v>
+      </c>
+      <c r="V89">
+        <v>9</v>
+      </c>
+      <c r="W89">
+        <v>8</v>
+      </c>
+      <c r="X89">
+        <v>9</v>
+      </c>
+      <c r="Y89">
+        <v>5</v>
+      </c>
+      <c r="Z89">
+        <v>6</v>
+      </c>
+      <c r="AA89">
+        <v>8</v>
+      </c>
+      <c r="AB89">
+        <v>10</v>
+      </c>
+      <c r="AC89">
+        <v>4</v>
+      </c>
+      <c r="AD89">
+        <v>9</v>
+      </c>
+      <c r="AE89">
+        <v>2</v>
+      </c>
+      <c r="AF89">
+        <v>5</v>
+      </c>
+      <c r="AG89">
+        <v>3</v>
+      </c>
+      <c r="AH89">
+        <v>4</v>
+      </c>
+      <c r="AI89">
+        <v>9</v>
+      </c>
+      <c r="AJ89">
+        <v>9</v>
+      </c>
+      <c r="AK89">
+        <v>1</v>
+      </c>
+      <c r="AL89">
+        <v>8</v>
+      </c>
+      <c r="AM89">
+        <v>9</v>
+      </c>
+      <c r="AN89">
+        <v>7</v>
+      </c>
+      <c r="AO89">
+        <v>4</v>
+      </c>
+      <c r="AP89">
+        <v>6</v>
+      </c>
+      <c r="AQ89">
+        <v>9</v>
+      </c>
+      <c r="AR89">
+        <v>6</v>
+      </c>
+      <c r="AS89">
+        <v>4</v>
+      </c>
+      <c r="AT89">
+        <v>2</v>
+      </c>
+      <c r="AU89">
+        <v>1</v>
+      </c>
+      <c r="AV89">
+        <v>2</v>
+      </c>
+      <c r="AW89">
+        <v>2</v>
+      </c>
+      <c r="AX89">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A90" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B90" t="s">
+        <v>74</v>
+      </c>
+      <c r="C90">
+        <v>7</v>
+      </c>
+      <c r="D90">
+        <v>3</v>
+      </c>
+      <c r="E90">
+        <v>9</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>9</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90">
+        <v>3</v>
+      </c>
+      <c r="J90">
+        <v>3</v>
+      </c>
+      <c r="K90">
+        <v>7</v>
+      </c>
+      <c r="L90">
+        <v>6</v>
+      </c>
+      <c r="M90">
+        <v>3</v>
+      </c>
+      <c r="N90">
+        <v>9</v>
+      </c>
+      <c r="O90">
+        <v>3</v>
+      </c>
+      <c r="P90">
+        <v>10</v>
+      </c>
+      <c r="Q90">
+        <v>9</v>
+      </c>
+      <c r="R90">
+        <v>6</v>
+      </c>
+      <c r="S90">
+        <v>8</v>
+      </c>
+      <c r="T90">
+        <v>4</v>
+      </c>
+      <c r="U90">
+        <v>1</v>
+      </c>
+      <c r="V90">
+        <v>8</v>
+      </c>
+      <c r="W90">
+        <v>7</v>
+      </c>
+      <c r="X90">
+        <v>9</v>
+      </c>
+      <c r="Y90">
+        <v>9</v>
+      </c>
+      <c r="Z90">
+        <v>4</v>
+      </c>
+      <c r="AA90">
+        <v>7</v>
+      </c>
+      <c r="AB90">
+        <v>10</v>
+      </c>
+      <c r="AC90">
+        <v>9</v>
+      </c>
+      <c r="AD90">
+        <v>5</v>
+      </c>
+      <c r="AE90">
+        <v>3</v>
+      </c>
+      <c r="AF90">
+        <v>6</v>
+      </c>
+      <c r="AG90">
+        <v>2</v>
+      </c>
+      <c r="AH90">
+        <v>1</v>
+      </c>
+      <c r="AI90">
+        <v>6</v>
+      </c>
+      <c r="AJ90">
+        <v>6</v>
+      </c>
+      <c r="AK90">
+        <v>2</v>
+      </c>
+      <c r="AL90">
+        <v>2</v>
+      </c>
+      <c r="AM90">
+        <v>6</v>
+      </c>
+      <c r="AN90">
+        <v>1</v>
+      </c>
+      <c r="AO90">
+        <v>2</v>
+      </c>
+      <c r="AP90">
+        <v>3</v>
+      </c>
+      <c r="AQ90">
+        <v>3</v>
+      </c>
+      <c r="AR90">
+        <v>2</v>
+      </c>
+      <c r="AS90">
+        <v>9</v>
+      </c>
+      <c r="AT90">
+        <v>8</v>
+      </c>
+      <c r="AU90">
+        <v>4</v>
+      </c>
+      <c r="AV90">
+        <v>10</v>
+      </c>
+      <c r="AW90">
+        <v>7</v>
+      </c>
+      <c r="AX90">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A91" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B91" t="s">
+        <v>74</v>
+      </c>
+      <c r="C91">
+        <v>6</v>
+      </c>
+      <c r="D91">
+        <v>10</v>
+      </c>
+      <c r="E91">
+        <v>4</v>
+      </c>
+      <c r="F91">
+        <v>9</v>
+      </c>
+      <c r="G91">
+        <v>8</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91">
+        <v>3</v>
+      </c>
+      <c r="J91">
+        <v>5</v>
+      </c>
+      <c r="K91">
+        <v>4</v>
+      </c>
+      <c r="L91">
+        <v>7</v>
+      </c>
+      <c r="M91">
+        <v>9</v>
+      </c>
+      <c r="N91">
+        <v>8</v>
+      </c>
+      <c r="O91">
+        <v>3</v>
+      </c>
+      <c r="P91">
+        <v>8</v>
+      </c>
+      <c r="Q91">
+        <v>7</v>
+      </c>
+      <c r="R91">
+        <v>5</v>
+      </c>
+      <c r="S91">
+        <v>10</v>
+      </c>
+      <c r="T91">
+        <v>9</v>
+      </c>
+      <c r="U91">
+        <v>6</v>
+      </c>
+      <c r="V91">
+        <v>2</v>
+      </c>
+      <c r="W91">
+        <v>3</v>
+      </c>
+      <c r="X91">
+        <v>6</v>
+      </c>
+      <c r="Y91">
+        <v>9</v>
+      </c>
+      <c r="Z91">
+        <v>1</v>
+      </c>
+      <c r="AA91">
+        <v>9</v>
+      </c>
+      <c r="AB91">
+        <v>10</v>
+      </c>
+      <c r="AC91">
+        <v>8</v>
+      </c>
+      <c r="AD91">
+        <v>9</v>
+      </c>
+      <c r="AE91">
+        <v>10</v>
+      </c>
+      <c r="AF91">
+        <v>1</v>
+      </c>
+      <c r="AG91">
+        <v>3</v>
+      </c>
+      <c r="AH91">
+        <v>6</v>
+      </c>
+      <c r="AI91">
+        <v>5</v>
+      </c>
+      <c r="AJ91">
+        <v>10</v>
+      </c>
+      <c r="AK91">
+        <v>9</v>
+      </c>
+      <c r="AL91">
+        <v>2</v>
+      </c>
+      <c r="AM91">
+        <v>4</v>
+      </c>
+      <c r="AN91">
+        <v>5</v>
+      </c>
+      <c r="AO91">
+        <v>1</v>
+      </c>
+      <c r="AP91">
+        <v>9</v>
+      </c>
+      <c r="AQ91">
+        <v>6</v>
+      </c>
+      <c r="AR91">
+        <v>2</v>
+      </c>
+      <c r="AS91">
+        <v>6</v>
+      </c>
+      <c r="AT91">
+        <v>3</v>
+      </c>
+      <c r="AU91">
+        <v>9</v>
+      </c>
+      <c r="AV91">
+        <v>1</v>
+      </c>
+      <c r="AW91">
+        <v>5</v>
+      </c>
+      <c r="AX91">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A92" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B92" t="s">
+        <v>74</v>
+      </c>
+      <c r="C92">
+        <v>10</v>
+      </c>
+      <c r="D92">
+        <v>4</v>
+      </c>
+      <c r="E92">
+        <v>7</v>
+      </c>
+      <c r="F92">
+        <v>6</v>
+      </c>
+      <c r="G92">
+        <v>5</v>
+      </c>
+      <c r="H92">
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <v>8</v>
+      </c>
+      <c r="J92">
+        <v>10</v>
+      </c>
+      <c r="K92">
+        <v>5</v>
+      </c>
+      <c r="L92">
+        <v>6</v>
+      </c>
+      <c r="M92">
+        <v>3</v>
+      </c>
+      <c r="N92">
+        <v>9</v>
+      </c>
+      <c r="O92">
+        <v>3</v>
+      </c>
+      <c r="P92">
+        <v>10</v>
+      </c>
+      <c r="Q92">
+        <v>5</v>
+      </c>
+      <c r="R92">
+        <v>3</v>
+      </c>
+      <c r="S92">
+        <v>7</v>
+      </c>
+      <c r="T92">
+        <v>3</v>
+      </c>
+      <c r="U92">
+        <v>8</v>
+      </c>
+      <c r="V92">
+        <v>10</v>
+      </c>
+      <c r="W92">
+        <v>5</v>
+      </c>
+      <c r="X92">
+        <v>5</v>
+      </c>
+      <c r="Y92">
+        <v>8</v>
+      </c>
+      <c r="Z92">
+        <v>3</v>
+      </c>
+      <c r="AA92">
+        <v>1</v>
+      </c>
+      <c r="AB92">
+        <v>6</v>
+      </c>
+      <c r="AC92">
+        <v>5</v>
+      </c>
+      <c r="AD92">
+        <v>9</v>
+      </c>
+      <c r="AE92">
+        <v>3</v>
+      </c>
+      <c r="AF92">
+        <v>5</v>
+      </c>
+      <c r="AG92">
+        <v>8</v>
+      </c>
+      <c r="AH92">
+        <v>5</v>
+      </c>
+      <c r="AI92">
+        <v>5</v>
+      </c>
+      <c r="AJ92">
+        <v>9</v>
+      </c>
+      <c r="AK92">
+        <v>8</v>
+      </c>
+      <c r="AL92">
+        <v>6</v>
+      </c>
+      <c r="AM92">
+        <v>3</v>
+      </c>
+      <c r="AN92">
+        <v>2</v>
+      </c>
+      <c r="AO92">
+        <v>4</v>
+      </c>
+      <c r="AP92">
+        <v>7</v>
+      </c>
+      <c r="AQ92">
+        <v>7</v>
+      </c>
+      <c r="AR92">
+        <v>3</v>
+      </c>
+      <c r="AS92">
+        <v>4</v>
+      </c>
+      <c r="AT92">
+        <v>6</v>
+      </c>
+      <c r="AU92">
+        <v>9</v>
+      </c>
+      <c r="AV92">
+        <v>8</v>
+      </c>
+      <c r="AW92">
+        <v>10</v>
+      </c>
+      <c r="AX92">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A93" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B93" t="s">
+        <v>74</v>
+      </c>
+      <c r="C93">
+        <v>3</v>
+      </c>
+      <c r="D93">
+        <v>8</v>
+      </c>
+      <c r="E93">
+        <v>3</v>
+      </c>
+      <c r="F93">
+        <v>5</v>
+      </c>
+      <c r="G93">
+        <v>2</v>
+      </c>
+      <c r="H93">
+        <v>6</v>
+      </c>
+      <c r="I93">
+        <v>5</v>
+      </c>
+      <c r="J93">
+        <v>10</v>
+      </c>
+      <c r="K93">
+        <v>2</v>
+      </c>
+      <c r="L93">
+        <v>9</v>
+      </c>
+      <c r="M93">
+        <v>6</v>
+      </c>
+      <c r="N93">
+        <v>1</v>
+      </c>
+      <c r="O93">
+        <v>2</v>
+      </c>
+      <c r="P93">
+        <v>9</v>
+      </c>
+      <c r="Q93">
+        <v>10</v>
+      </c>
+      <c r="R93">
+        <v>3</v>
+      </c>
+      <c r="S93">
+        <v>5</v>
+      </c>
+      <c r="T93">
+        <v>8</v>
+      </c>
+      <c r="U93">
+        <v>7</v>
+      </c>
+      <c r="V93">
+        <v>9</v>
+      </c>
+      <c r="W93">
+        <v>6</v>
+      </c>
+      <c r="X93">
+        <v>2</v>
+      </c>
+      <c r="Y93">
+        <v>2</v>
+      </c>
+      <c r="Z93">
+        <v>5</v>
+      </c>
+      <c r="AA93">
+        <v>7</v>
+      </c>
+      <c r="AB93">
+        <v>7</v>
+      </c>
+      <c r="AC93">
+        <v>10</v>
+      </c>
+      <c r="AD93">
+        <v>2</v>
+      </c>
+      <c r="AE93">
+        <v>9</v>
+      </c>
+      <c r="AF93">
+        <v>8</v>
+      </c>
+      <c r="AG93">
+        <v>10</v>
+      </c>
+      <c r="AH93">
+        <v>1</v>
+      </c>
+      <c r="AI93">
+        <v>5</v>
+      </c>
+      <c r="AJ93">
+        <v>4</v>
+      </c>
+      <c r="AK93">
+        <v>9</v>
+      </c>
+      <c r="AL93">
+        <v>3</v>
+      </c>
+      <c r="AM93">
+        <v>8</v>
+      </c>
+      <c r="AN93">
+        <v>7</v>
+      </c>
+      <c r="AO93">
+        <v>9</v>
+      </c>
+      <c r="AP93">
+        <v>9</v>
+      </c>
+      <c r="AQ93">
+        <v>4</v>
+      </c>
+      <c r="AR93">
+        <v>9</v>
+      </c>
+      <c r="AS93">
+        <v>6</v>
+      </c>
+      <c r="AT93">
+        <v>10</v>
+      </c>
+      <c r="AU93">
+        <v>3</v>
+      </c>
+      <c r="AV93">
+        <v>5</v>
+      </c>
+      <c r="AW93">
+        <v>2</v>
+      </c>
+      <c r="AX93">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A94" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B94" t="s">
+        <v>74</v>
+      </c>
+      <c r="C94">
+        <v>2</v>
+      </c>
+      <c r="D94">
+        <v>6</v>
+      </c>
+      <c r="E94">
+        <v>4</v>
+      </c>
+      <c r="F94">
+        <v>10</v>
+      </c>
+      <c r="G94">
+        <v>10</v>
+      </c>
+      <c r="H94">
+        <v>2</v>
+      </c>
+      <c r="I94">
+        <v>10</v>
+      </c>
+      <c r="J94">
+        <v>5</v>
+      </c>
+      <c r="K94">
+        <v>5</v>
+      </c>
+      <c r="L94">
+        <v>3</v>
+      </c>
+      <c r="M94">
+        <v>7</v>
+      </c>
+      <c r="N94">
+        <v>6</v>
+      </c>
+      <c r="O94">
+        <v>8</v>
+      </c>
+      <c r="P94">
+        <v>9</v>
+      </c>
+      <c r="Q94">
+        <v>8</v>
+      </c>
+      <c r="R94">
+        <v>8</v>
+      </c>
+      <c r="S94">
+        <v>10</v>
+      </c>
+      <c r="T94">
+        <v>8</v>
+      </c>
+      <c r="U94">
+        <v>9</v>
+      </c>
+      <c r="V94">
+        <v>3</v>
+      </c>
+      <c r="W94">
+        <v>6</v>
+      </c>
+      <c r="X94">
+        <v>1</v>
+      </c>
+      <c r="Y94">
+        <v>7</v>
+      </c>
+      <c r="Z94">
+        <v>2</v>
+      </c>
+      <c r="AA94">
+        <v>7</v>
+      </c>
+      <c r="AB94">
+        <v>10</v>
+      </c>
+      <c r="AC94">
+        <v>8</v>
+      </c>
+      <c r="AD94">
+        <v>2</v>
+      </c>
+      <c r="AE94">
+        <v>3</v>
+      </c>
+      <c r="AF94">
+        <v>7</v>
+      </c>
+      <c r="AG94">
+        <v>10</v>
+      </c>
+      <c r="AH94">
+        <v>8</v>
+      </c>
+      <c r="AI94">
+        <v>9</v>
+      </c>
+      <c r="AJ94">
+        <v>1</v>
+      </c>
+      <c r="AK94">
+        <v>8</v>
+      </c>
+      <c r="AL94">
+        <v>1</v>
+      </c>
+      <c r="AM94">
+        <v>8</v>
+      </c>
+      <c r="AN94">
+        <v>8</v>
+      </c>
+      <c r="AO94">
+        <v>9</v>
+      </c>
+      <c r="AP94">
+        <v>1</v>
+      </c>
+      <c r="AQ94">
+        <v>4</v>
+      </c>
+      <c r="AR94">
+        <v>9</v>
+      </c>
+      <c r="AS94">
+        <v>2</v>
+      </c>
+      <c r="AT94">
+        <v>6</v>
+      </c>
+      <c r="AU94">
+        <v>2</v>
+      </c>
+      <c r="AV94">
+        <v>10</v>
+      </c>
+      <c r="AW94">
+        <v>9</v>
+      </c>
+      <c r="AX94">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A95" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B95" t="s">
+        <v>74</v>
+      </c>
+      <c r="C95">
+        <v>9</v>
+      </c>
+      <c r="D95">
+        <v>10</v>
+      </c>
+      <c r="E95">
+        <v>8</v>
+      </c>
+      <c r="F95">
+        <v>5</v>
+      </c>
+      <c r="G95">
+        <v>2</v>
+      </c>
+      <c r="H95">
+        <v>3</v>
+      </c>
+      <c r="I95">
+        <v>8</v>
+      </c>
+      <c r="J95">
+        <v>3</v>
+      </c>
+      <c r="K95">
+        <v>2</v>
+      </c>
+      <c r="L95">
+        <v>10</v>
+      </c>
+      <c r="M95">
+        <v>1</v>
+      </c>
+      <c r="N95">
+        <v>9</v>
+      </c>
+      <c r="O95">
+        <v>7</v>
+      </c>
+      <c r="P95">
+        <v>6</v>
+      </c>
+      <c r="Q95">
+        <v>6</v>
+      </c>
+      <c r="R95">
+        <v>1</v>
+      </c>
+      <c r="S95">
+        <v>5</v>
+      </c>
+      <c r="T95">
+        <v>6</v>
+      </c>
+      <c r="U95">
+        <v>8</v>
+      </c>
+      <c r="V95">
+        <v>4</v>
+      </c>
+      <c r="W95">
+        <v>3</v>
+      </c>
+      <c r="X95">
+        <v>1</v>
+      </c>
+      <c r="Y95">
+        <v>3</v>
+      </c>
+      <c r="Z95">
+        <v>3</v>
+      </c>
+      <c r="AA95">
+        <v>4</v>
+      </c>
+      <c r="AB95">
+        <v>6</v>
+      </c>
+      <c r="AC95">
+        <v>9</v>
+      </c>
+      <c r="AD95">
+        <v>3</v>
+      </c>
+      <c r="AE95">
+        <v>5</v>
+      </c>
+      <c r="AF95">
+        <v>3</v>
+      </c>
+      <c r="AG95">
+        <v>1</v>
+      </c>
+      <c r="AH95">
+        <v>9</v>
+      </c>
+      <c r="AI95">
+        <v>9</v>
+      </c>
+      <c r="AJ95">
+        <v>4</v>
+      </c>
+      <c r="AK95">
+        <v>3</v>
+      </c>
+      <c r="AL95">
+        <v>4</v>
+      </c>
+      <c r="AM95">
+        <v>2</v>
+      </c>
+      <c r="AN95">
+        <v>8</v>
+      </c>
+      <c r="AO95">
+        <v>7</v>
+      </c>
+      <c r="AP95">
+        <v>1</v>
+      </c>
+      <c r="AQ95">
+        <v>8</v>
+      </c>
+      <c r="AR95">
+        <v>7</v>
+      </c>
+      <c r="AS95">
+        <v>1</v>
+      </c>
+      <c r="AT95">
+        <v>3</v>
+      </c>
+      <c r="AU95">
+        <v>7</v>
+      </c>
+      <c r="AV95">
+        <v>5</v>
+      </c>
+      <c r="AW95">
+        <v>4</v>
+      </c>
+      <c r="AX95">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A96" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B96" t="s">
+        <v>74</v>
+      </c>
+      <c r="C96">
+        <v>6</v>
+      </c>
+      <c r="D96">
+        <v>7</v>
+      </c>
+      <c r="E96">
+        <v>10</v>
+      </c>
+      <c r="F96">
+        <v>8</v>
+      </c>
+      <c r="G96">
+        <v>7</v>
+      </c>
+      <c r="H96">
+        <v>7</v>
+      </c>
+      <c r="I96">
+        <v>4</v>
+      </c>
+      <c r="J96">
+        <v>6</v>
+      </c>
+      <c r="K96">
+        <v>1</v>
+      </c>
+      <c r="L96">
+        <v>9</v>
+      </c>
+      <c r="M96">
+        <v>8</v>
+      </c>
+      <c r="N96">
+        <v>6</v>
+      </c>
+      <c r="O96">
+        <v>2</v>
+      </c>
+      <c r="P96">
+        <v>3</v>
+      </c>
+      <c r="Q96">
+        <v>8</v>
+      </c>
+      <c r="R96">
+        <v>2</v>
+      </c>
+      <c r="S96">
+        <v>6</v>
+      </c>
+      <c r="T96">
+        <v>8</v>
+      </c>
+      <c r="U96">
+        <v>7</v>
+      </c>
+      <c r="V96">
+        <v>4</v>
+      </c>
+      <c r="W96">
+        <v>5</v>
+      </c>
+      <c r="X96">
+        <v>10</v>
+      </c>
+      <c r="Y96">
+        <v>9</v>
+      </c>
+      <c r="Z96">
+        <v>10</v>
+      </c>
+      <c r="AA96">
+        <v>10</v>
+      </c>
+      <c r="AB96">
+        <v>8</v>
+      </c>
+      <c r="AC96">
+        <v>4</v>
+      </c>
+      <c r="AD96">
+        <v>3</v>
+      </c>
+      <c r="AE96">
+        <v>9</v>
+      </c>
+      <c r="AF96">
+        <v>6</v>
+      </c>
+      <c r="AG96">
+        <v>10</v>
+      </c>
+      <c r="AH96">
+        <v>8</v>
+      </c>
+      <c r="AI96">
+        <v>10</v>
+      </c>
+      <c r="AJ96">
+        <v>7</v>
+      </c>
+      <c r="AK96">
+        <v>10</v>
+      </c>
+      <c r="AL96">
+        <v>1</v>
+      </c>
+      <c r="AM96">
+        <v>4</v>
+      </c>
+      <c r="AN96">
+        <v>6</v>
+      </c>
+      <c r="AO96">
+        <v>1</v>
+      </c>
+      <c r="AP96">
+        <v>5</v>
+      </c>
+      <c r="AQ96">
+        <v>7</v>
+      </c>
+      <c r="AR96">
+        <v>8</v>
+      </c>
+      <c r="AS96">
+        <v>2</v>
+      </c>
+      <c r="AT96">
+        <v>3</v>
+      </c>
+      <c r="AU96">
+        <v>4</v>
+      </c>
+      <c r="AV96">
+        <v>7</v>
+      </c>
+      <c r="AW96">
+        <v>2</v>
+      </c>
+      <c r="AX96">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A97" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B97" t="s">
+        <v>74</v>
+      </c>
+      <c r="C97">
+        <v>8</v>
+      </c>
+      <c r="D97">
+        <v>9</v>
+      </c>
+      <c r="E97">
+        <v>7</v>
+      </c>
+      <c r="F97">
+        <v>10</v>
+      </c>
+      <c r="G97">
+        <v>4</v>
+      </c>
+      <c r="H97">
+        <v>4</v>
+      </c>
+      <c r="I97">
+        <v>9</v>
+      </c>
+      <c r="J97">
+        <v>4</v>
+      </c>
+      <c r="K97">
+        <v>4</v>
+      </c>
+      <c r="L97">
+        <v>8</v>
+      </c>
+      <c r="M97">
+        <v>2</v>
+      </c>
+      <c r="N97">
+        <v>2</v>
+      </c>
+      <c r="O97">
+        <v>6</v>
+      </c>
+      <c r="P97">
+        <v>4</v>
+      </c>
+      <c r="Q97">
+        <v>4</v>
+      </c>
+      <c r="R97">
+        <v>3</v>
+      </c>
+      <c r="S97">
+        <v>6</v>
+      </c>
+      <c r="T97">
+        <v>7</v>
+      </c>
+      <c r="U97">
+        <v>2</v>
+      </c>
+      <c r="V97">
+        <v>6</v>
+      </c>
+      <c r="W97">
+        <v>3</v>
+      </c>
+      <c r="X97">
+        <v>9</v>
+      </c>
+      <c r="Y97">
+        <v>7</v>
+      </c>
+      <c r="Z97">
+        <v>2</v>
+      </c>
+      <c r="AA97">
+        <v>4</v>
+      </c>
+      <c r="AB97">
+        <v>3</v>
+      </c>
+      <c r="AC97">
+        <v>6</v>
+      </c>
+      <c r="AD97">
+        <v>4</v>
+      </c>
+      <c r="AE97">
+        <v>10</v>
+      </c>
+      <c r="AF97">
+        <v>8</v>
+      </c>
+      <c r="AG97">
+        <v>10</v>
+      </c>
+      <c r="AH97">
+        <v>10</v>
+      </c>
+      <c r="AI97">
+        <v>4</v>
+      </c>
+      <c r="AJ97">
+        <v>1</v>
+      </c>
+      <c r="AK97">
+        <v>8</v>
+      </c>
+      <c r="AL97">
+        <v>9</v>
+      </c>
+      <c r="AM97">
+        <v>2</v>
+      </c>
+      <c r="AN97">
+        <v>9</v>
+      </c>
+      <c r="AO97">
+        <v>9</v>
+      </c>
+      <c r="AP97">
+        <v>4</v>
+      </c>
+      <c r="AQ97">
+        <v>1</v>
+      </c>
+      <c r="AR97">
+        <v>10</v>
+      </c>
+      <c r="AS97">
+        <v>7</v>
+      </c>
+      <c r="AT97">
+        <v>10</v>
+      </c>
+      <c r="AU97">
+        <v>9</v>
+      </c>
+      <c r="AV97">
+        <v>2</v>
+      </c>
+      <c r="AW97">
+        <v>4</v>
+      </c>
+      <c r="AX97">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A98" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B98" t="s">
+        <v>74</v>
+      </c>
+      <c r="C98">
+        <v>4</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98">
+        <v>7</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98">
+        <v>7</v>
+      </c>
+      <c r="I98">
+        <v>8</v>
+      </c>
+      <c r="J98">
+        <v>9</v>
+      </c>
+      <c r="K98">
+        <v>2</v>
+      </c>
+      <c r="L98">
+        <v>4</v>
+      </c>
+      <c r="M98">
+        <v>8</v>
+      </c>
+      <c r="N98">
+        <v>8</v>
+      </c>
+      <c r="O98">
+        <v>5</v>
+      </c>
+      <c r="P98">
+        <v>4</v>
+      </c>
+      <c r="Q98">
+        <v>1</v>
+      </c>
+      <c r="R98">
+        <v>6</v>
+      </c>
+      <c r="S98">
+        <v>2</v>
+      </c>
+      <c r="T98">
+        <v>4</v>
+      </c>
+      <c r="U98">
+        <v>4</v>
+      </c>
+      <c r="V98">
+        <v>5</v>
+      </c>
+      <c r="W98">
+        <v>10</v>
+      </c>
+      <c r="X98">
+        <v>9</v>
+      </c>
+      <c r="Y98">
+        <v>7</v>
+      </c>
+      <c r="Z98">
+        <v>5</v>
+      </c>
+      <c r="AA98">
+        <v>6</v>
+      </c>
+      <c r="AB98">
+        <v>5</v>
+      </c>
+      <c r="AC98">
+        <v>10</v>
+      </c>
+      <c r="AD98">
+        <v>4</v>
+      </c>
+      <c r="AE98">
+        <v>6</v>
+      </c>
+      <c r="AF98">
+        <v>7</v>
+      </c>
+      <c r="AG98">
+        <v>1</v>
+      </c>
+      <c r="AH98">
+        <v>10</v>
+      </c>
+      <c r="AI98">
+        <v>10</v>
+      </c>
+      <c r="AJ98">
+        <v>3</v>
+      </c>
+      <c r="AK98">
+        <v>3</v>
+      </c>
+      <c r="AL98">
+        <v>8</v>
+      </c>
+      <c r="AM98">
+        <v>9</v>
+      </c>
+      <c r="AN98">
+        <v>1</v>
+      </c>
+      <c r="AO98">
+        <v>1</v>
+      </c>
+      <c r="AP98">
+        <v>1</v>
+      </c>
+      <c r="AQ98">
+        <v>6</v>
+      </c>
+      <c r="AR98">
+        <v>6</v>
+      </c>
+      <c r="AS98">
+        <v>5</v>
+      </c>
+      <c r="AT98">
+        <v>3</v>
+      </c>
+      <c r="AU98">
+        <v>4</v>
+      </c>
+      <c r="AV98">
+        <v>3</v>
+      </c>
+      <c r="AW98">
+        <v>2</v>
+      </c>
+      <c r="AX98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A99" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B99" t="s">
+        <v>74</v>
+      </c>
+      <c r="C99">
+        <v>7</v>
+      </c>
+      <c r="D99">
+        <v>5</v>
+      </c>
+      <c r="E99">
+        <v>3</v>
+      </c>
+      <c r="F99">
+        <v>7</v>
+      </c>
+      <c r="G99">
+        <v>7</v>
+      </c>
+      <c r="H99">
+        <v>7</v>
+      </c>
+      <c r="I99">
+        <v>10</v>
+      </c>
+      <c r="J99">
+        <v>2</v>
+      </c>
+      <c r="K99">
+        <v>4</v>
+      </c>
+      <c r="L99">
+        <v>10</v>
+      </c>
+      <c r="M99">
+        <v>5</v>
+      </c>
+      <c r="N99">
+        <v>3</v>
+      </c>
+      <c r="O99">
+        <v>5</v>
+      </c>
+      <c r="P99">
+        <v>9</v>
+      </c>
+      <c r="Q99">
+        <v>6</v>
+      </c>
+      <c r="R99">
+        <v>9</v>
+      </c>
+      <c r="S99">
+        <v>4</v>
+      </c>
+      <c r="T99">
+        <v>10</v>
+      </c>
+      <c r="U99">
+        <v>5</v>
+      </c>
+      <c r="V99">
+        <v>1</v>
+      </c>
+      <c r="W99">
+        <v>3</v>
+      </c>
+      <c r="X99">
+        <v>4</v>
+      </c>
+      <c r="Y99">
+        <v>9</v>
+      </c>
+      <c r="Z99">
+        <v>2</v>
+      </c>
+      <c r="AA99">
+        <v>5</v>
+      </c>
+      <c r="AB99">
+        <v>9</v>
+      </c>
+      <c r="AC99">
+        <v>1</v>
+      </c>
+      <c r="AD99">
+        <v>5</v>
+      </c>
+      <c r="AE99">
+        <v>8</v>
+      </c>
+      <c r="AF99">
+        <v>4</v>
+      </c>
+      <c r="AG99">
+        <v>10</v>
+      </c>
+      <c r="AH99">
+        <v>2</v>
+      </c>
+      <c r="AI99">
+        <v>6</v>
+      </c>
+      <c r="AJ99">
+        <v>4</v>
+      </c>
+      <c r="AK99">
+        <v>1</v>
+      </c>
+      <c r="AL99">
+        <v>2</v>
+      </c>
+      <c r="AM99">
+        <v>7</v>
+      </c>
+      <c r="AN99">
+        <v>6</v>
+      </c>
+      <c r="AO99">
+        <v>4</v>
+      </c>
+      <c r="AP99">
+        <v>7</v>
+      </c>
+      <c r="AQ99">
+        <v>9</v>
+      </c>
+      <c r="AR99">
+        <v>7</v>
+      </c>
+      <c r="AS99">
+        <v>3</v>
+      </c>
+      <c r="AT99">
+        <v>5</v>
+      </c>
+      <c r="AU99">
+        <v>3</v>
+      </c>
+      <c r="AV99">
+        <v>8</v>
+      </c>
+      <c r="AW99">
+        <v>3</v>
+      </c>
+      <c r="AX99">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A100" s="1">
+        <v>46167.500057870369</v>
+      </c>
+      <c r="B100" t="s">
+        <v>74</v>
+      </c>
+      <c r="C100">
+        <v>9</v>
+      </c>
+      <c r="D100">
+        <v>2</v>
+      </c>
+      <c r="E100">
+        <v>8</v>
+      </c>
+      <c r="F100">
+        <v>3</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>6</v>
+      </c>
+      <c r="I100">
+        <v>6</v>
+      </c>
+      <c r="J100">
+        <v>8</v>
+      </c>
+      <c r="K100">
+        <v>9</v>
+      </c>
+      <c r="L100">
+        <v>5</v>
+      </c>
+      <c r="M100">
+        <v>2</v>
+      </c>
+      <c r="N100">
+        <v>2</v>
+      </c>
+      <c r="O100">
+        <v>4</v>
+      </c>
+      <c r="P100">
+        <v>6</v>
+      </c>
+      <c r="Q100">
+        <v>8</v>
+      </c>
+      <c r="R100">
+        <v>4</v>
+      </c>
+      <c r="S100">
+        <v>4</v>
+      </c>
+      <c r="T100">
+        <v>8</v>
+      </c>
+      <c r="U100">
+        <v>5</v>
+      </c>
+      <c r="V100">
+        <v>4</v>
+      </c>
+      <c r="W100">
+        <v>9</v>
+      </c>
+      <c r="X100">
+        <v>7</v>
+      </c>
+      <c r="Y100">
+        <v>3</v>
+      </c>
+      <c r="Z100">
+        <v>10</v>
+      </c>
+      <c r="AA100">
+        <v>5</v>
+      </c>
+      <c r="AB100">
+        <v>2</v>
+      </c>
+      <c r="AC100">
+        <v>5</v>
+      </c>
+      <c r="AD100">
+        <v>4</v>
+      </c>
+      <c r="AE100">
+        <v>9</v>
+      </c>
+      <c r="AF100">
+        <v>7</v>
+      </c>
+      <c r="AG100">
+        <v>9</v>
+      </c>
+      <c r="AH100">
+        <v>1</v>
+      </c>
+      <c r="AI100">
+        <v>5</v>
+      </c>
+      <c r="AJ100">
+        <v>7</v>
+      </c>
+      <c r="AK100">
+        <v>3</v>
+      </c>
+      <c r="AL100">
+        <v>2</v>
+      </c>
+      <c r="AM100">
+        <v>3</v>
+      </c>
+      <c r="AN100">
+        <v>4</v>
+      </c>
+      <c r="AO100">
+        <v>10</v>
+      </c>
+      <c r="AP100">
+        <v>5</v>
+      </c>
+      <c r="AQ100">
+        <v>8</v>
+      </c>
+      <c r="AR100">
+        <v>3</v>
+      </c>
+      <c r="AS100">
+        <v>9</v>
+      </c>
+      <c r="AT100">
+        <v>8</v>
+      </c>
+      <c r="AU100">
+        <v>7</v>
+      </c>
+      <c r="AV100">
+        <v>10</v>
+      </c>
+      <c r="AW100">
+        <v>2</v>
+      </c>
+      <c r="AX100">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
